--- a/youzi/屠文斌/index.xlsx
+++ b/youzi/屠文斌/index.xlsx
@@ -45,13 +45,217 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,7 +273,1921 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56E79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56E79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4DAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,13 +2199,757 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC82C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4856"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,42 +2961,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -147,19 +2973,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,175 +3183,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D9DC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,67 +3345,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56C77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -423,73 +3483,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -501,127 +3531,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -633,139 +3561,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -814,2838 +3646,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56E79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56E79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4DAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4856"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56C77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D9DC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -10026,7 +10026,7 @@
       <c r="C2" t="str">
         <v>002575</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="8" t="str">
         <v>净买: 1374.90万</v>
       </c>
       <c r="E2">
@@ -10041,40 +10041,40 @@
       <c r="H2">
         <v>-2.88</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="5">
         <v>-7.29</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="12">
         <v>-4.78</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="13">
         <v>-5.92</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="2">
         <v>-6.72</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="9">
         <v>2.62</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="6">
         <v>1.82</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="10">
         <v>6.83</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="1">
         <v>17.54</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="7">
         <v>29.27</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="3">
         <v>42.26</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="4">
         <v>47.04</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="11">
         <v>-25.51</v>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       <c r="C3" t="str">
         <v>002575</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -2672.88万</v>
       </c>
       <c r="E3">
@@ -10103,40 +10103,40 @@
       <c r="H3">
         <v>9.98</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="18">
         <v>0</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="23">
         <v>10.04</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="19">
         <v>13.74</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="20">
         <v>2.38</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="14">
         <v>12.6</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="21">
         <v>1.32</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="15">
         <v>-8.28</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="16">
         <v>-6.78</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="22">
         <v>-7.05</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="24">
         <v>-15.42</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="25">
         <v>-13.13</v>
       </c>
-      <c r="T3" s="18">
+      <c r="T3" s="26">
         <v>-42.38</v>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       <c r="C4" t="str">
         <v>605303</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="39" t="str">
         <v>净买: 323.34万</v>
       </c>
       <c r="E4">
@@ -10165,40 +10165,40 @@
       <c r="H4">
         <v>-2.55</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="27">
         <v>-4.97</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="28">
         <v>-5.15</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="35">
         <v>-6.78</v>
       </c>
       <c r="L4" s="36">
         <v>-8.31</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="32">
         <v>-9.49</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="30">
         <v>-10.39</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="29">
         <v>-13.37</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="33">
         <v>-12.74</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="37">
         <v>-14.27</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="31">
         <v>-15.54</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="34">
         <v>-16.71</v>
       </c>
-      <c r="T4" s="35">
+      <c r="T4" s="38">
         <v>120.78</v>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       <c r="C5" t="str">
         <v>600590</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="50" t="str">
         <v>净买: 7131.26万</v>
       </c>
       <c r="E5">
@@ -10227,40 +10227,40 @@
       <c r="H5">
         <v>0.17</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="43">
         <v>-8.07</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="44">
         <v>-10.84</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="51">
         <v>-10.84</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="52">
         <v>-15.88</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="45">
         <v>-19.75</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="48">
         <v>-27.73</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="40">
         <v>-25.21</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="46">
         <v>-17.73</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="49">
         <v>-19.5</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="41">
         <v>-11.43</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="42">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="51">
+      <c r="T5" s="47">
         <v>33.11</v>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       <c r="C6" t="str">
         <v>600063</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="59" t="str">
         <v>净买: 2621.63万</v>
       </c>
       <c r="E6">
@@ -10289,40 +10289,40 @@
       <c r="H6">
         <v>4.82</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="53">
         <v>5.03</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="54">
         <v>0</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="63">
         <v>1.53</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="60">
         <v>2.84</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="64">
         <v>2.63</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="61">
         <v>1.09</v>
       </c>
       <c r="O6" s="55">
         <v>0.22</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="58">
         <v>2.84</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="65">
         <v>2.84</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="56">
         <v>1.97</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="57">
         <v>0.88</v>
       </c>
-      <c r="T6" s="60">
+      <c r="T6" s="62">
         <v>53.83</v>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       <c r="C7" t="str">
         <v>002300</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -2462.36万</v>
       </c>
       <c r="E7">
@@ -10351,40 +10351,40 @@
       <c r="H7">
         <v>0.65</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="68">
         <v>9.34</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="69">
         <v>-0.91</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="75">
         <v>-10.77</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="77">
         <v>-17.64</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="78">
         <v>-19.97</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="70">
         <v>-20.88</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="66">
         <v>-21.66</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="71">
         <v>-29.44</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="76">
         <v>-31.39</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="72">
         <v>-28.92</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="74">
         <v>-27.63</v>
       </c>
-      <c r="T7" s="76">
+      <c r="T7" s="67">
         <v>22.83</v>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       <c r="C8" t="str">
         <v>605133</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="84" t="str">
         <v>净卖: -2062.31万</v>
       </c>
       <c r="E8">
@@ -10413,37 +10413,37 @@
       <c r="H8">
         <v>1.83</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="87">
         <v>7.94</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="85">
         <v>5.89</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="79">
         <v>7.6</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="80">
         <v>8.82</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="88">
         <v>19.7</v>
       </c>
-      <c r="N8" s="87">
+      <c r="N8" s="82">
         <v>31.67</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="86">
         <v>32.52</v>
       </c>
       <c r="P8" s="89">
         <v>21.71</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="83">
         <v>26.06</v>
       </c>
       <c r="R8" s="90">
         <v>28.27</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="81">
         <v>31.3</v>
       </c>
       <c r="T8" s="91">
@@ -10460,7 +10460,7 @@
       <c r="C9" t="str">
         <v>600187</v>
       </c>
-      <c r="D9" s="99" t="str">
+      <c r="D9" s="97" t="str">
         <v>净买: 91.44万</v>
       </c>
       <c r="E9">
@@ -10475,40 +10475,40 @@
       <c r="H9">
         <v>-9.97</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="92">
         <v>0</v>
       </c>
       <c r="J9" s="93">
         <v>-9.62</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="98">
         <v>-13.12</v>
       </c>
-      <c r="L9" s="100">
+      <c r="L9" s="103">
         <v>-14.29</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="94">
         <v>-10.5</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="95">
         <v>-6.12</v>
       </c>
-      <c r="O9" s="97">
+      <c r="O9" s="102">
         <v>-6.71</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="96">
         <v>-6.71</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="99">
         <v>-7.58</v>
       </c>
-      <c r="R9" s="103">
+      <c r="R9" s="104">
         <v>-7</v>
       </c>
-      <c r="S9" s="92">
+      <c r="S9" s="100">
         <v>-6.71</v>
       </c>
-      <c r="T9" s="98">
+      <c r="T9" s="101">
         <v>-47.23</v>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       <c r="C10" t="str">
         <v>600439</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="117" t="str">
         <v>净买: 1007.14万</v>
       </c>
       <c r="E10">
@@ -10537,40 +10537,40 @@
       <c r="H10">
         <v>-9.46</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="108">
         <v>-0.6</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="109">
         <v>-2.69</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="110">
         <v>-3.58</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="105">
         <v>-5.97</v>
       </c>
-      <c r="M10" s="110">
+      <c r="M10" s="111">
         <v>-5.97</v>
       </c>
-      <c r="N10" s="114">
+      <c r="N10" s="106">
         <v>-5.67</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="116">
         <v>-5.37</v>
       </c>
-      <c r="P10" s="111">
+      <c r="P10" s="107">
         <v>-5.07</v>
       </c>
-      <c r="Q10" s="116">
+      <c r="Q10" s="112">
         <v>-5.97</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="113">
         <v>-6.57</v>
       </c>
-      <c r="S10" s="112">
+      <c r="S10" s="114">
         <v>-5.67</v>
       </c>
-      <c r="T10" s="105">
+      <c r="T10" s="115">
         <v>-24.48</v>
       </c>
     </row>
@@ -10599,37 +10599,37 @@
       <c r="H11">
         <v>0.28</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="120">
         <v>9.68</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="130">
         <v>20.62</v>
       </c>
       <c r="K11" s="121">
         <v>18.58</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="125">
         <v>17.88</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="126">
         <v>20.97</v>
       </c>
-      <c r="N11" s="126">
+      <c r="N11" s="127">
         <v>33.1</v>
       </c>
-      <c r="O11" s="124">
+      <c r="O11" s="118">
         <v>34.78</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="128">
         <v>33.38</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="119">
         <v>33.1</v>
       </c>
-      <c r="R11" s="120">
+      <c r="R11" s="123">
         <v>35.27</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="124">
         <v>38.15</v>
       </c>
       <c r="T11" s="129">
@@ -10646,7 +10646,7 @@
       <c r="C12" t="str">
         <v>002148</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="135" t="str">
         <v>净卖: -7676.21万</v>
       </c>
       <c r="E12">
@@ -10661,40 +10661,40 @@
       <c r="H12">
         <v>8.07</v>
       </c>
-      <c r="I12" s="134">
+      <c r="I12" s="131">
         <v>1.78</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="136">
         <v>12</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="140">
         <v>14.13</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="141">
         <v>18.67</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="137">
         <v>24.62</v>
       </c>
-      <c r="N12" s="136">
+      <c r="N12" s="142">
         <v>12.53</v>
       </c>
       <c r="O12" s="143">
         <v>11.82</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="132">
         <v>10.04</v>
       </c>
-      <c r="Q12" s="141">
+      <c r="Q12" s="138">
         <v>5.42</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="139">
         <v>4</v>
       </c>
-      <c r="S12" s="137">
+      <c r="S12" s="133">
         <v>2.31</v>
       </c>
-      <c r="T12" s="138">
+      <c r="T12" s="134">
         <v>-30.76</v>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       <c r="C13" t="str">
         <v>002148</v>
       </c>
-      <c r="D13" s="151" t="str">
+      <c r="D13" s="155" t="str">
         <v>净卖: -7781.22万</v>
       </c>
       <c r="E13">
@@ -10723,40 +10723,40 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="153">
         <v>10.04</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="147">
         <v>12.14</v>
       </c>
-      <c r="K13" s="144">
+      <c r="K13" s="156">
         <v>16.59</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="144">
         <v>22.45</v>
       </c>
       <c r="M13" s="148">
         <v>10.57</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="150">
         <v>9.87</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="151">
         <v>8.12</v>
       </c>
-      <c r="P13" s="149">
+      <c r="P13" s="145">
         <v>3.58</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="152">
         <v>2.18</v>
       </c>
-      <c r="R13" s="154">
+      <c r="R13" s="149">
         <v>0.52</v>
       </c>
-      <c r="S13" s="150">
+      <c r="S13" s="146">
         <v>0.61</v>
       </c>
-      <c r="T13" s="155">
+      <c r="T13" s="154">
         <v>-31.97</v>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       <c r="C14" t="str">
         <v>000700</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="163" t="str">
         <v>净买: 6133.53万</v>
       </c>
       <c r="E14">
@@ -10785,16 +10785,16 @@
       <c r="H14">
         <v>3.92</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="159">
         <v>5.83</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="164">
         <v>4.1</v>
       </c>
-      <c r="K14" s="160">
+      <c r="K14" s="165">
         <v>1.94</v>
       </c>
-      <c r="L14" s="161">
+      <c r="L14" s="160">
         <v>2.05</v>
       </c>
       <c r="M14" s="166">
@@ -10803,22 +10803,22 @@
       <c r="N14" s="162">
         <v>2.91</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="167">
         <v>5.61</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="161">
         <v>3.67</v>
       </c>
-      <c r="Q14" s="164">
+      <c r="Q14" s="168">
         <v>4.31</v>
       </c>
-      <c r="R14" s="167">
+      <c r="R14" s="169">
         <v>5.18</v>
       </c>
-      <c r="S14" s="165">
+      <c r="S14" s="157">
         <v>6.26</v>
       </c>
-      <c r="T14" s="157">
+      <c r="T14" s="158">
         <v>26.54</v>
       </c>
     </row>
@@ -10832,7 +10832,7 @@
       <c r="C15" t="str">
         <v>603222</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="176" t="str">
         <v>净买: 2341.28万</v>
       </c>
       <c r="E15">
@@ -10847,40 +10847,40 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="180">
+      <c r="I15" s="177">
         <v>0</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="178">
         <v>10.02</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="179">
         <v>5.75</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="172">
         <v>-4.82</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="175">
         <v>-8.26</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="180">
         <v>-15.31</v>
       </c>
-      <c r="O15" s="181">
+      <c r="O15" s="182">
         <v>-6.86</v>
       </c>
-      <c r="P15" s="172">
+      <c r="P15" s="170">
         <v>2.41</v>
       </c>
-      <c r="Q15" s="178">
+      <c r="Q15" s="173">
         <v>6.86</v>
       </c>
-      <c r="R15" s="175">
+      <c r="R15" s="181">
         <v>17.53</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="171">
         <v>5.75</v>
       </c>
-      <c r="T15" s="176">
+      <c r="T15" s="174">
         <v>-2.23</v>
       </c>
     </row>
@@ -10894,7 +10894,7 @@
       <c r="C16" t="str">
         <v>603222</v>
       </c>
-      <c r="D16" s="187" t="str">
+      <c r="D16" s="186" t="str">
         <v>净买: 2384.77万</v>
       </c>
       <c r="E16">
@@ -10909,40 +10909,40 @@
       <c r="H16">
         <v>-2.63</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="187">
         <v>-7.57</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="188">
         <v>-10.9</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="192">
         <v>-17.75</v>
       </c>
-      <c r="L16" s="189">
+      <c r="L16" s="193">
         <v>-9.55</v>
       </c>
-      <c r="M16" s="192">
+      <c r="M16" s="183">
         <v>-0.54</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="184">
         <v>3.78</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="189">
         <v>14.14</v>
       </c>
-      <c r="P16" s="195">
+      <c r="P16" s="191">
         <v>2.7</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="194">
         <v>-5.68</v>
       </c>
-      <c r="R16" s="186">
+      <c r="R16" s="195">
         <v>3.78</v>
       </c>
-      <c r="S16" s="183">
+      <c r="S16" s="190">
         <v>-5.32</v>
       </c>
-      <c r="T16" s="190">
+      <c r="T16" s="185">
         <v>-5.05</v>
       </c>
     </row>
@@ -10956,7 +10956,7 @@
       <c r="C17" t="str">
         <v>603222</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="208" t="str">
         <v>净卖: -1529.63万</v>
       </c>
       <c r="E17">
@@ -10971,10 +10971,10 @@
       <c r="H17">
         <v>-3.39</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="201">
         <v>13.81</v>
       </c>
-      <c r="J17" s="201">
+      <c r="J17" s="196">
         <v>18.76</v>
       </c>
       <c r="K17" s="205">
@@ -10983,28 +10983,28 @@
       <c r="L17" s="206">
         <v>17.53</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="197">
         <v>7.94</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="198">
         <v>18.76</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="203">
         <v>8.35</v>
       </c>
-      <c r="P17" s="202">
+      <c r="P17" s="207">
         <v>19.18</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="202">
         <v>29.38</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="204">
         <v>31.75</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="199">
         <v>44.95</v>
       </c>
-      <c r="T17" s="198">
+      <c r="T17" s="200">
         <v>8.66</v>
       </c>
     </row>
@@ -11018,7 +11018,7 @@
       <c r="C18" t="str">
         <v>600330</v>
       </c>
-      <c r="D18" s="221" t="str">
+      <c r="D18" s="220" t="str">
         <v>净卖: -5410.71万</v>
       </c>
       <c r="E18">
@@ -11033,40 +11033,40 @@
       <c r="H18">
         <v>10</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="211">
         <v>-5.66</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="218">
         <v>3.77</v>
       </c>
       <c r="K18" s="214">
         <v>-0.51</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="221">
         <v>-7.72</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="219">
         <v>-10.89</v>
       </c>
       <c r="N18" s="215">
         <v>-6.43</v>
       </c>
-      <c r="O18" s="217">
+      <c r="O18" s="209">
         <v>-8.23</v>
       </c>
-      <c r="P18" s="212">
+      <c r="P18" s="216">
         <v>-3.77</v>
       </c>
-      <c r="Q18" s="218">
+      <c r="Q18" s="210">
         <v>-2.23</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="217">
         <v>-1.63</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="212">
         <v>-0.77</v>
       </c>
-      <c r="T18" s="220">
+      <c r="T18" s="213">
         <v>86.36</v>
       </c>
     </row>
@@ -11095,40 +11095,40 @@
       <c r="H19">
         <v>-0.06</v>
       </c>
-      <c r="I19" s="228">
+      <c r="I19" s="230">
         <v>20.07</v>
       </c>
-      <c r="J19" s="225">
+      <c r="J19" s="222">
         <v>35.34</v>
       </c>
-      <c r="K19" s="226">
+      <c r="K19" s="228">
         <v>35.22</v>
       </c>
       <c r="L19" s="229">
         <v>46.33</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="223">
         <v>43.45</v>
       </c>
       <c r="N19" s="231">
         <v>51.86</v>
       </c>
-      <c r="O19" s="230">
+      <c r="O19" s="224">
         <v>52.76</v>
       </c>
       <c r="P19" s="232">
         <v>39.24</v>
       </c>
-      <c r="Q19" s="227">
+      <c r="Q19" s="225">
         <v>39.12</v>
       </c>
-      <c r="R19" s="223">
+      <c r="R19" s="233">
         <v>39.48</v>
       </c>
-      <c r="S19" s="233">
+      <c r="S19" s="226">
         <v>35.58</v>
       </c>
-      <c r="T19" s="224">
+      <c r="T19" s="227">
         <v>86.72</v>
       </c>
     </row>
@@ -11157,40 +11157,40 @@
       <c r="H20">
         <v>9.99</v>
       </c>
-      <c r="I20" s="237">
+      <c r="I20" s="245">
         <v>0</v>
       </c>
-      <c r="J20" s="241">
+      <c r="J20" s="240">
         <v>-10</v>
       </c>
-      <c r="K20" s="245">
+      <c r="K20" s="241">
         <v>-11.75</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="242">
         <v>-15.79</v>
       </c>
-      <c r="M20" s="238">
+      <c r="M20" s="247">
         <v>-17.23</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="237">
         <v>-18.88</v>
       </c>
-      <c r="O20" s="242">
+      <c r="O20" s="246">
         <v>-19.34</v>
       </c>
-      <c r="P20" s="243">
+      <c r="P20" s="238">
         <v>-20.05</v>
       </c>
-      <c r="Q20" s="247">
+      <c r="Q20" s="239">
         <v>-18.83</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="243">
         <v>-19.44</v>
       </c>
       <c r="S20" s="235">
         <v>-21.88</v>
       </c>
-      <c r="T20" s="240">
+      <c r="T20" s="236">
         <v>-30.33</v>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
       <c r="C21" t="str">
         <v>000988</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="248" t="str">
         <v>净买: 3.56亿</v>
       </c>
       <c r="E21">
@@ -11219,40 +11219,40 @@
       <c r="H21">
         <v>1.87</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="252">
         <v>3.48</v>
       </c>
       <c r="J21" s="249">
         <v>3.58</v>
       </c>
-      <c r="K21" s="254">
+      <c r="K21" s="253">
         <v>8.96</v>
       </c>
-      <c r="L21" s="255">
+      <c r="L21" s="254">
         <v>11.51</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="257">
         <v>16.03</v>
       </c>
-      <c r="N21" s="258">
+      <c r="N21" s="250">
         <v>17.6</v>
       </c>
-      <c r="O21" s="257">
+      <c r="O21" s="260">
         <v>12.38</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="258">
         <v>13.08</v>
       </c>
-      <c r="Q21" s="252">
+      <c r="Q21" s="259">
         <v>24.39</v>
       </c>
-      <c r="R21" s="260">
+      <c r="R21" s="251">
         <v>17.41</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="255">
         <v>26.26</v>
       </c>
-      <c r="T21" s="250">
+      <c r="T21" s="256">
         <v>48.58</v>
       </c>
     </row>
@@ -11266,7 +11266,7 @@
       <c r="C22" t="str">
         <v>300507</v>
       </c>
-      <c r="D22" s="266" t="str">
+      <c r="D22" s="271" t="str">
         <v>净买: 6982.34万</v>
       </c>
       <c r="E22">
@@ -11281,40 +11281,40 @@
       <c r="H22">
         <v>0.23</v>
       </c>
-      <c r="I22" s="263">
+      <c r="I22" s="267">
         <v>19.72</v>
       </c>
-      <c r="J22" s="271">
+      <c r="J22" s="272">
         <v>17.09</v>
       </c>
-      <c r="K22" s="272">
+      <c r="K22" s="273">
         <v>15.6</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="261">
         <v>16.28</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="270">
         <v>17.32</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="264">
         <v>12.39</v>
       </c>
-      <c r="O22" s="261">
+      <c r="O22" s="262">
         <v>11.24</v>
       </c>
-      <c r="P22" s="268">
+      <c r="P22" s="265">
         <v>8.94</v>
       </c>
-      <c r="Q22" s="262">
+      <c r="Q22" s="266">
         <v>7.57</v>
       </c>
-      <c r="R22" s="269">
+      <c r="R22" s="268">
         <v>18.35</v>
       </c>
-      <c r="S22" s="270">
+      <c r="S22" s="269">
         <v>15.94</v>
       </c>
-      <c r="T22" s="273">
+      <c r="T22" s="263">
         <v>1.61</v>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       <c r="C23" t="str">
         <v>000988</v>
       </c>
-      <c r="D23" s="274" t="str">
+      <c r="D23" s="275" t="str">
         <v>净买: 1.74亿</v>
       </c>
       <c r="E23">
@@ -11343,40 +11343,40 @@
       <c r="H23">
         <v>2.59</v>
       </c>
-      <c r="I23" s="275">
+      <c r="I23" s="276">
         <v>7.22</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="284">
         <v>1.21</v>
       </c>
-      <c r="K23" s="284">
+      <c r="K23" s="282">
         <v>8.84</v>
       </c>
-      <c r="L23" s="280">
+      <c r="L23" s="277">
         <v>1.51</v>
       </c>
-      <c r="M23" s="286">
+      <c r="M23" s="285">
         <v>-2.95</v>
       </c>
-      <c r="N23" s="281">
+      <c r="N23" s="286">
         <v>-6.43</v>
       </c>
-      <c r="O23" s="277">
+      <c r="O23" s="278">
         <v>-9.42</v>
       </c>
-      <c r="P23" s="282">
+      <c r="P23" s="279">
         <v>-13.77</v>
       </c>
-      <c r="Q23" s="278">
+      <c r="Q23" s="283">
         <v>-11.78</v>
       </c>
-      <c r="R23" s="285">
+      <c r="R23" s="280">
         <v>-11.13</v>
       </c>
-      <c r="S23" s="279">
+      <c r="S23" s="274">
         <v>-14.93</v>
       </c>
-      <c r="T23" s="283">
+      <c r="T23" s="281">
         <v>28.08</v>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       <c r="C24" t="str">
         <v>300948</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="298" t="str">
         <v>净卖: -57.39万</v>
       </c>
       <c r="E24">
@@ -11405,40 +11405,40 @@
       <c r="H24">
         <v>20</v>
       </c>
-      <c r="I24" s="290">
+      <c r="I24" s="291">
         <v>0</v>
       </c>
-      <c r="J24" s="295">
+      <c r="J24" s="297">
         <v>20.01</v>
       </c>
-      <c r="K24" s="291">
+      <c r="K24" s="288">
         <v>44.05</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="292">
         <v>63.39</v>
       </c>
-      <c r="M24" s="297">
+      <c r="M24" s="299">
         <v>37.5</v>
       </c>
-      <c r="N24" s="298">
+      <c r="N24" s="293">
         <v>46.5</v>
       </c>
-      <c r="O24" s="299">
+      <c r="O24" s="294">
         <v>45.24</v>
       </c>
-      <c r="P24" s="292">
+      <c r="P24" s="287">
         <v>49.55</v>
       </c>
-      <c r="Q24" s="293">
+      <c r="Q24" s="295">
         <v>42.04</v>
       </c>
-      <c r="R24" s="287">
+      <c r="R24" s="296">
         <v>36.61</v>
       </c>
-      <c r="S24" s="288">
+      <c r="S24" s="289">
         <v>63.91</v>
       </c>
-      <c r="T24" s="289">
+      <c r="T24" s="290">
         <v>43.6</v>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
       <c r="C25" t="str">
         <v>000988</v>
       </c>
-      <c r="D25" s="300" t="str">
+      <c r="D25" s="301" t="str">
         <v>净卖: -1.91亿</v>
       </c>
       <c r="E25">
@@ -11467,40 +11467,40 @@
       <c r="H25">
         <v>1.05</v>
       </c>
-      <c r="I25" s="301">
+      <c r="I25" s="308">
         <v>-7.7</v>
       </c>
-      <c r="J25" s="302">
+      <c r="J25" s="311">
         <v>-11.76</v>
       </c>
-      <c r="K25" s="303">
+      <c r="K25" s="312">
         <v>-14.92</v>
       </c>
-      <c r="L25" s="308">
+      <c r="L25" s="305">
         <v>-17.64</v>
       </c>
-      <c r="M25" s="304">
+      <c r="M25" s="306">
         <v>-21.59</v>
       </c>
-      <c r="N25" s="309">
+      <c r="N25" s="300">
         <v>-19.78</v>
       </c>
-      <c r="O25" s="306">
+      <c r="O25" s="307">
         <v>-19.19</v>
       </c>
-      <c r="P25" s="305">
+      <c r="P25" s="309">
         <v>-22.65</v>
       </c>
-      <c r="Q25" s="310">
+      <c r="Q25" s="302">
         <v>-20.41</v>
       </c>
-      <c r="R25" s="311">
+      <c r="R25" s="310">
         <v>-17.38</v>
       </c>
-      <c r="S25" s="307">
+      <c r="S25" s="303">
         <v>-15</v>
       </c>
-      <c r="T25" s="312">
+      <c r="T25" s="304">
         <v>16.46</v>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       <c r="C26" t="str">
         <v>600067</v>
       </c>
-      <c r="D26" s="323" t="str">
+      <c r="D26" s="322" t="str">
         <v>净买: 785.29万</v>
       </c>
       <c r="E26">
@@ -11529,40 +11529,40 @@
       <c r="H26">
         <v>4.48</v>
       </c>
-      <c r="I26" s="321">
+      <c r="I26" s="320">
         <v>5.36</v>
       </c>
-      <c r="J26" s="324">
+      <c r="J26" s="314">
         <v>8.85</v>
       </c>
-      <c r="K26" s="316">
+      <c r="K26" s="321">
         <v>19.84</v>
       </c>
-      <c r="L26" s="320">
+      <c r="L26" s="315">
         <v>19.3</v>
       </c>
-      <c r="M26" s="317">
+      <c r="M26" s="323">
         <v>10.19</v>
       </c>
-      <c r="N26" s="318">
+      <c r="N26" s="317">
         <v>11.53</v>
       </c>
-      <c r="O26" s="322">
+      <c r="O26" s="318">
         <v>22.79</v>
       </c>
-      <c r="P26" s="325">
+      <c r="P26" s="324">
         <v>28.42</v>
       </c>
-      <c r="Q26" s="313">
+      <c r="Q26" s="325">
         <v>26.01</v>
       </c>
-      <c r="R26" s="314">
+      <c r="R26" s="313">
         <v>30.56</v>
       </c>
-      <c r="S26" s="315">
+      <c r="S26" s="319">
         <v>35.66</v>
       </c>
-      <c r="T26" s="319">
+      <c r="T26" s="316">
         <v>10.72</v>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       <c r="C27" t="str">
         <v>300102</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="335" t="str">
         <v>净买: 5184.05万</v>
       </c>
       <c r="E27">
@@ -11591,40 +11591,40 @@
       <c r="H27">
         <v>13.28</v>
       </c>
-      <c r="I27" s="331">
+      <c r="I27" s="333">
         <v>5.94</v>
       </c>
       <c r="J27" s="327">
         <v>16.67</v>
       </c>
-      <c r="K27" s="332">
+      <c r="K27" s="329">
         <v>22.39</v>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="330">
         <v>10.78</v>
       </c>
-      <c r="M27" s="335">
+      <c r="M27" s="336">
         <v>16.44</v>
       </c>
-      <c r="N27" s="328">
+      <c r="N27" s="337">
         <v>32.67</v>
       </c>
-      <c r="O27" s="329">
+      <c r="O27" s="338">
         <v>31.06</v>
       </c>
-      <c r="P27" s="330">
+      <c r="P27" s="331">
         <v>46</v>
       </c>
-      <c r="Q27" s="338">
+      <c r="Q27" s="326">
         <v>44</v>
       </c>
-      <c r="R27" s="333">
+      <c r="R27" s="332">
         <v>41.67</v>
       </c>
-      <c r="S27" s="326">
+      <c r="S27" s="328">
         <v>46.22</v>
       </c>
-      <c r="T27" s="336">
+      <c r="T27" s="334">
         <v>82.78</v>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
       <c r="C28" t="str">
         <v>688239</v>
       </c>
-      <c r="D28" s="350" t="str">
+      <c r="D28" s="345" t="str">
         <v>净买: 1.73亿</v>
       </c>
       <c r="E28">
@@ -11653,40 +11653,40 @@
       <c r="H28">
         <v>0.62</v>
       </c>
-      <c r="I28" s="351">
+      <c r="I28" s="340">
         <v>19.11</v>
       </c>
-      <c r="J28" s="339">
+      <c r="J28" s="346">
         <v>13.38</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="347">
         <v>10.24</v>
       </c>
-      <c r="L28" s="347">
+      <c r="L28" s="341">
         <v>10.39</v>
       </c>
       <c r="M28" s="348">
         <v>6.52</v>
       </c>
-      <c r="N28" s="340">
+      <c r="N28" s="349">
         <v>7.9</v>
       </c>
-      <c r="O28" s="345">
+      <c r="O28" s="342">
         <v>7.76</v>
       </c>
-      <c r="P28" s="349">
+      <c r="P28" s="350">
         <v>4.43</v>
       </c>
-      <c r="Q28" s="341">
+      <c r="Q28" s="351">
         <v>9.54</v>
       </c>
-      <c r="R28" s="344">
+      <c r="R28" s="339">
         <v>11.84</v>
       </c>
-      <c r="S28" s="342">
+      <c r="S28" s="343">
         <v>15.56</v>
       </c>
-      <c r="T28" s="343">
+      <c r="T28" s="344">
         <v>11.18</v>
       </c>
     </row>
@@ -11715,40 +11715,40 @@
       <c r="H29">
         <v>6.98</v>
       </c>
-      <c r="I29" s="352">
+      <c r="I29" s="354">
         <v>2.83</v>
       </c>
-      <c r="J29" s="360">
+      <c r="J29" s="355">
         <v>13.12</v>
       </c>
-      <c r="K29" s="361">
+      <c r="K29" s="360">
         <v>1.81</v>
       </c>
-      <c r="L29" s="353">
+      <c r="L29" s="364">
         <v>-0.51</v>
       </c>
-      <c r="M29" s="354">
+      <c r="M29" s="352">
         <v>-2.1</v>
       </c>
-      <c r="N29" s="355">
+      <c r="N29" s="356">
         <v>-1.88</v>
       </c>
-      <c r="O29" s="357">
+      <c r="O29" s="353">
         <v>-1.59</v>
       </c>
       <c r="P29" s="363">
         <v>-3.91</v>
       </c>
-      <c r="Q29" s="356">
+      <c r="Q29" s="357">
         <v>-3.41</v>
       </c>
-      <c r="R29" s="362">
+      <c r="R29" s="361">
         <v>-2.46</v>
       </c>
       <c r="S29" s="358">
         <v>-1.96</v>
       </c>
-      <c r="T29" s="364">
+      <c r="T29" s="362">
         <v>5.43</v>
       </c>
     </row>
@@ -11762,7 +11762,7 @@
       <c r="C30" t="str">
         <v>300102</v>
       </c>
-      <c r="D30" s="377" t="str">
+      <c r="D30" s="374" t="str">
         <v>净卖: -1.54亿</v>
       </c>
       <c r="E30">
@@ -11777,40 +11777,40 @@
       <c r="H30">
         <v>8.69</v>
       </c>
-      <c r="I30" s="365">
+      <c r="I30" s="375">
         <v>10.41</v>
       </c>
-      <c r="J30" s="373">
+      <c r="J30" s="368">
         <v>14.72</v>
       </c>
-      <c r="K30" s="366">
+      <c r="K30" s="376">
         <v>5.96</v>
       </c>
-      <c r="L30" s="374">
+      <c r="L30" s="369">
         <v>2.21</v>
       </c>
-      <c r="M30" s="367">
+      <c r="M30" s="377">
         <v>-3.33</v>
       </c>
-      <c r="N30" s="370">
+      <c r="N30" s="365">
         <v>-2.48</v>
       </c>
-      <c r="O30" s="375">
+      <c r="O30" s="372">
         <v>0.97</v>
       </c>
-      <c r="P30" s="371">
+      <c r="P30" s="370">
         <v>-6.08</v>
       </c>
-      <c r="Q30" s="368">
+      <c r="Q30" s="366">
         <v>-8.26</v>
       </c>
-      <c r="R30" s="376">
+      <c r="R30" s="371">
         <v>-3.72</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="367">
         <v>15.55</v>
       </c>
-      <c r="T30" s="372">
+      <c r="T30" s="373">
         <v>-2.95</v>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       <c r="C31" t="str">
         <v>300830</v>
       </c>
-      <c r="D31" s="386" t="str">
+      <c r="D31" s="385" t="str">
         <v>净买: 5772.47万</v>
       </c>
       <c r="E31">
@@ -11839,40 +11839,40 @@
       <c r="H31">
         <v>7.44</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="386">
         <v>11.69</v>
       </c>
-      <c r="J31" s="383">
+      <c r="J31" s="378">
         <v>5.08</v>
       </c>
-      <c r="K31" s="387">
+      <c r="K31" s="379">
         <v>7.69</v>
       </c>
-      <c r="L31" s="388">
+      <c r="L31" s="387">
         <v>-1.38</v>
       </c>
-      <c r="M31" s="384">
+      <c r="M31" s="388">
         <v>-5.85</v>
       </c>
-      <c r="N31" s="379">
+      <c r="N31" s="389">
         <v>-4.77</v>
       </c>
       <c r="O31" s="380">
         <v>-0.92</v>
       </c>
-      <c r="P31" s="385">
+      <c r="P31" s="381">
         <v>7.31</v>
       </c>
-      <c r="Q31" s="389">
+      <c r="Q31" s="382">
         <v>8.38</v>
       </c>
-      <c r="R31" s="381">
+      <c r="R31" s="383">
         <v>13.62</v>
       </c>
-      <c r="S31" s="390">
+      <c r="S31" s="384">
         <v>17.38</v>
       </c>
-      <c r="T31" s="378">
+      <c r="T31" s="390">
         <v>-15.85</v>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       <c r="C32" t="str">
         <v>002181</v>
       </c>
-      <c r="D32" s="399" t="str">
+      <c r="D32" s="401" t="str">
         <v>净买: 3260.12万</v>
       </c>
       <c r="E32">
@@ -11901,40 +11901,40 @@
       <c r="H32">
         <v>2.98</v>
       </c>
-      <c r="I32" s="392">
+      <c r="I32" s="396">
         <v>6.84</v>
       </c>
-      <c r="J32" s="401">
+      <c r="J32" s="393">
         <v>1.16</v>
       </c>
-      <c r="K32" s="393">
+      <c r="K32" s="402">
         <v>11.27</v>
       </c>
-      <c r="L32" s="394">
+      <c r="L32" s="397">
         <v>5.49</v>
       </c>
-      <c r="M32" s="395">
+      <c r="M32" s="398">
         <v>2.22</v>
       </c>
-      <c r="N32" s="402">
+      <c r="N32" s="403">
         <v>-2.02</v>
       </c>
-      <c r="O32" s="403">
+      <c r="O32" s="391">
         <v>7.8</v>
       </c>
-      <c r="P32" s="396">
+      <c r="P32" s="392">
         <v>11.85</v>
       </c>
-      <c r="Q32" s="391">
+      <c r="Q32" s="394">
         <v>16.28</v>
       </c>
-      <c r="R32" s="400">
+      <c r="R32" s="395">
         <v>12.52</v>
       </c>
-      <c r="S32" s="398">
+      <c r="S32" s="399">
         <v>13.1</v>
       </c>
-      <c r="T32" s="397">
+      <c r="T32" s="400">
         <v>32.08</v>
       </c>
     </row>
@@ -11948,7 +11948,7 @@
       <c r="C33" t="str">
         <v>300229</v>
       </c>
-      <c r="D33" s="408" t="str">
+      <c r="D33" s="416" t="str">
         <v>净买: 1.91亿</v>
       </c>
       <c r="E33">
@@ -11963,7 +11963,7 @@
       <c r="H33">
         <v>-2.13</v>
       </c>
-      <c r="I33" s="409">
+      <c r="I33" s="410">
         <v>17.73</v>
       </c>
       <c r="J33" s="413">
@@ -11972,31 +11972,31 @@
       <c r="K33" s="404">
         <v>-4.16</v>
       </c>
-      <c r="L33" s="405">
+      <c r="L33" s="411">
         <v>-6.48</v>
       </c>
-      <c r="M33" s="414">
+      <c r="M33" s="405">
         <v>-8.77</v>
       </c>
-      <c r="N33" s="415">
+      <c r="N33" s="406">
         <v>-9.65</v>
       </c>
-      <c r="O33" s="410">
+      <c r="O33" s="407">
         <v>-8.58</v>
       </c>
-      <c r="P33" s="416">
+      <c r="P33" s="408">
         <v>-6.37</v>
       </c>
-      <c r="Q33" s="406">
+      <c r="Q33" s="409">
         <v>-9.15</v>
       </c>
       <c r="R33" s="412">
         <v>-7.43</v>
       </c>
-      <c r="S33" s="407">
+      <c r="S33" s="414">
         <v>-11.25</v>
       </c>
-      <c r="T33" s="411">
+      <c r="T33" s="415">
         <v>-28.67</v>
       </c>
     </row>
@@ -12010,7 +12010,7 @@
       <c r="C34" t="str">
         <v>603311</v>
       </c>
-      <c r="D34" s="421" t="str">
+      <c r="D34" s="426" t="str">
         <v>净卖: -911.79万</v>
       </c>
       <c r="E34">
@@ -12025,40 +12025,40 @@
       <c r="H34">
         <v>0.6</v>
       </c>
-      <c r="I34" s="426">
+      <c r="I34" s="421">
         <v>9.37</v>
       </c>
-      <c r="J34" s="424">
+      <c r="J34" s="422">
         <v>8.11</v>
       </c>
-      <c r="K34" s="425">
+      <c r="K34" s="427">
         <v>5.58</v>
       </c>
-      <c r="L34" s="419">
+      <c r="L34" s="425">
         <v>5.91</v>
       </c>
-      <c r="M34" s="420">
+      <c r="M34" s="417">
         <v>5.65</v>
       </c>
-      <c r="N34" s="427">
+      <c r="N34" s="428">
         <v>3.46</v>
       </c>
-      <c r="O34" s="422">
+      <c r="O34" s="423">
         <v>8.04</v>
       </c>
-      <c r="P34" s="428">
+      <c r="P34" s="418">
         <v>7.84</v>
       </c>
-      <c r="Q34" s="423">
+      <c r="Q34" s="419">
         <v>6.51</v>
       </c>
-      <c r="R34" s="429">
+      <c r="R34" s="420">
         <v>6.51</v>
       </c>
-      <c r="S34" s="417">
+      <c r="S34" s="424">
         <v>4.52</v>
       </c>
-      <c r="T34" s="418">
+      <c r="T34" s="429">
         <v>32.23</v>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
       <c r="C35" t="str">
         <v>002279</v>
       </c>
-      <c r="D35" s="433" t="str">
+      <c r="D35" s="434" t="str">
         <v>净买: 4355.47万</v>
       </c>
       <c r="E35">
@@ -12087,40 +12087,40 @@
       <c r="H35">
         <v>3.46</v>
       </c>
-      <c r="I35" s="439">
+      <c r="I35" s="440">
         <v>6.29</v>
       </c>
-      <c r="J35" s="434">
+      <c r="J35" s="435">
         <v>4.36</v>
       </c>
-      <c r="K35" s="438">
+      <c r="K35" s="436">
         <v>2.43</v>
       </c>
-      <c r="L35" s="440">
+      <c r="L35" s="441">
         <v>9.74</v>
       </c>
-      <c r="M35" s="441">
+      <c r="M35" s="442">
         <v>4.77</v>
       </c>
-      <c r="N35" s="442">
+      <c r="N35" s="437">
         <v>8.01</v>
       </c>
-      <c r="O35" s="435">
+      <c r="O35" s="438">
         <v>3.85</v>
       </c>
-      <c r="P35" s="436">
+      <c r="P35" s="430">
         <v>2.03</v>
       </c>
-      <c r="Q35" s="430">
+      <c r="Q35" s="431">
         <v>5.78</v>
       </c>
-      <c r="R35" s="437">
+      <c r="R35" s="439">
         <v>1.93</v>
       </c>
-      <c r="S35" s="431">
+      <c r="S35" s="432">
         <v>0.61</v>
       </c>
-      <c r="T35" s="432">
+      <c r="T35" s="433">
         <v>-17.04</v>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       <c r="C36" t="str">
         <v>002115</v>
       </c>
-      <c r="D36" s="445" t="str">
+      <c r="D36" s="453" t="str">
         <v>净卖: -7662.33万</v>
       </c>
       <c r="E36">
@@ -12149,40 +12149,40 @@
       <c r="H36">
         <v>1.82</v>
       </c>
-      <c r="I36" s="446">
+      <c r="I36" s="444">
         <v>5.92</v>
       </c>
-      <c r="J36" s="450">
+      <c r="J36" s="454">
         <v>-1.58</v>
       </c>
-      <c r="K36" s="451">
+      <c r="K36" s="448">
         <v>8.26</v>
       </c>
-      <c r="L36" s="452">
+      <c r="L36" s="449">
         <v>6.06</v>
       </c>
-      <c r="M36" s="443">
+      <c r="M36" s="445">
         <v>8.05</v>
       </c>
-      <c r="N36" s="444">
+      <c r="N36" s="450">
         <v>2.75</v>
       </c>
-      <c r="O36" s="454">
+      <c r="O36" s="446">
         <v>0.48</v>
       </c>
-      <c r="P36" s="447">
+      <c r="P36" s="451">
         <v>7.02</v>
       </c>
-      <c r="Q36" s="453">
+      <c r="Q36" s="455">
         <v>5.3</v>
       </c>
-      <c r="R36" s="448">
+      <c r="R36" s="452">
         <v>3.44</v>
       </c>
-      <c r="S36" s="449">
+      <c r="S36" s="443">
         <v>0.34</v>
       </c>
-      <c r="T36" s="455">
+      <c r="T36" s="447">
         <v>-13.49</v>
       </c>
     </row>
@@ -12196,7 +12196,7 @@
       <c r="C37" t="str">
         <v>300063</v>
       </c>
-      <c r="D37" s="468" t="str">
+      <c r="D37" s="462" t="str">
         <v>净买: 7192.18万</v>
       </c>
       <c r="E37">
@@ -12211,40 +12211,40 @@
       <c r="H37">
         <v>-4.19</v>
       </c>
-      <c r="I37" s="456">
+      <c r="I37" s="467">
         <v>25.24</v>
       </c>
-      <c r="J37" s="458">
+      <c r="J37" s="468">
         <v>19.99</v>
       </c>
-      <c r="K37" s="466">
+      <c r="K37" s="463">
         <v>21.66</v>
       </c>
-      <c r="L37" s="467">
+      <c r="L37" s="456">
         <v>29.47</v>
       </c>
-      <c r="M37" s="459">
+      <c r="M37" s="464">
         <v>19.11</v>
       </c>
-      <c r="N37" s="461">
+      <c r="N37" s="457">
         <v>13.2</v>
       </c>
-      <c r="O37" s="462">
+      <c r="O37" s="460">
         <v>10.5</v>
       </c>
-      <c r="P37" s="463">
+      <c r="P37" s="461">
         <v>19.99</v>
       </c>
-      <c r="Q37" s="464">
+      <c r="Q37" s="458">
         <v>15.68</v>
       </c>
-      <c r="R37" s="465">
+      <c r="R37" s="459">
         <v>10.14</v>
       </c>
-      <c r="S37" s="460">
+      <c r="S37" s="465">
         <v>8.97</v>
       </c>
-      <c r="T37" s="457">
+      <c r="T37" s="466">
         <v>-10.87</v>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       <c r="C38" t="str">
         <v>300063</v>
       </c>
-      <c r="D38" s="474" t="str">
+      <c r="D38" s="469" t="str">
         <v>净卖: -4187.17万</v>
       </c>
       <c r="E38">
@@ -12273,40 +12273,40 @@
       <c r="H38">
         <v>0.73</v>
       </c>
-      <c r="I38" s="481">
+      <c r="I38" s="478">
         <v>0.66</v>
       </c>
-      <c r="J38" s="475">
+      <c r="J38" s="470">
         <v>7.12</v>
       </c>
-      <c r="K38" s="476">
+      <c r="K38" s="471">
         <v>-1.45</v>
       </c>
-      <c r="L38" s="469">
+      <c r="L38" s="472">
         <v>-6.34</v>
       </c>
-      <c r="M38" s="477">
+      <c r="M38" s="479">
         <v>-8.57</v>
       </c>
-      <c r="N38" s="472">
+      <c r="N38" s="480">
         <v>-0.72</v>
       </c>
-      <c r="O38" s="470">
+      <c r="O38" s="473">
         <v>-4.28</v>
       </c>
-      <c r="P38" s="479">
+      <c r="P38" s="474">
         <v>-8.87</v>
       </c>
-      <c r="Q38" s="473">
+      <c r="Q38" s="476">
         <v>-9.84</v>
       </c>
-      <c r="R38" s="478">
+      <c r="R38" s="475">
         <v>-13.88</v>
       </c>
-      <c r="S38" s="471">
+      <c r="S38" s="481">
         <v>-14.67</v>
       </c>
-      <c r="T38" s="480">
+      <c r="T38" s="477">
         <v>-26.25</v>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
       <c r="C39" t="str">
         <v>603103</v>
       </c>
-      <c r="D39" s="488" t="str">
+      <c r="D39" s="493" t="str">
         <v>净买: 513.73万</v>
       </c>
       <c r="E39">
@@ -12335,37 +12335,37 @@
       <c r="H39">
         <v>-10</v>
       </c>
-      <c r="I39" s="493">
+      <c r="I39" s="494">
         <v>0</v>
       </c>
-      <c r="J39" s="494">
+      <c r="J39" s="482">
         <v>-6.9</v>
       </c>
-      <c r="K39" s="490">
+      <c r="K39" s="487">
         <v>-6.72</v>
       </c>
-      <c r="L39" s="482">
+      <c r="L39" s="488">
         <v>-10.65</v>
       </c>
-      <c r="M39" s="491">
+      <c r="M39" s="483">
         <v>-13.72</v>
       </c>
-      <c r="N39" s="489">
+      <c r="N39" s="490">
         <v>-12.84</v>
       </c>
-      <c r="O39" s="484">
+      <c r="O39" s="491">
         <v>-13.23</v>
       </c>
-      <c r="P39" s="483">
+      <c r="P39" s="484">
         <v>-12.03</v>
       </c>
-      <c r="Q39" s="485">
+      <c r="Q39" s="489">
         <v>-11.64</v>
       </c>
-      <c r="R39" s="486">
+      <c r="R39" s="485">
         <v>-12.98</v>
       </c>
-      <c r="S39" s="487">
+      <c r="S39" s="486">
         <v>-13.62</v>
       </c>
       <c r="T39" s="492">
@@ -12382,7 +12382,7 @@
       <c r="C40" t="str">
         <v>300830</v>
       </c>
-      <c r="D40" s="500" t="str">
+      <c r="D40" s="496" t="str">
         <v>净卖: -2824.56万</v>
       </c>
       <c r="E40">
@@ -12397,40 +12397,40 @@
       <c r="H40">
         <v>3.71</v>
       </c>
-      <c r="I40" s="505">
+      <c r="I40" s="502">
         <v>15.71</v>
       </c>
-      <c r="J40" s="501">
+      <c r="J40" s="503">
         <v>10.42</v>
       </c>
-      <c r="K40" s="502">
+      <c r="K40" s="497">
         <v>3.42</v>
       </c>
-      <c r="L40" s="506">
+      <c r="L40" s="504">
         <v>5.52</v>
       </c>
-      <c r="M40" s="496">
+      <c r="M40" s="498">
         <v>2.18</v>
       </c>
-      <c r="N40" s="497">
+      <c r="N40" s="505">
         <v>10.96</v>
       </c>
-      <c r="O40" s="507">
+      <c r="O40" s="499">
         <v>10.03</v>
       </c>
-      <c r="P40" s="498">
+      <c r="P40" s="506">
         <v>10.11</v>
       </c>
-      <c r="Q40" s="503">
+      <c r="Q40" s="500">
         <v>10.42</v>
       </c>
-      <c r="R40" s="495">
+      <c r="R40" s="501">
         <v>5.37</v>
       </c>
-      <c r="S40" s="504">
+      <c r="S40" s="507">
         <v>0.39</v>
       </c>
-      <c r="T40" s="499">
+      <c r="T40" s="495">
         <v>-14.93</v>
       </c>
     </row>
@@ -12444,7 +12444,7 @@
       <c r="C41" t="str">
         <v>600135</v>
       </c>
-      <c r="D41" s="516" t="str">
+      <c r="D41" s="519" t="str">
         <v>净买: 5244.18万</v>
       </c>
       <c r="E41">
@@ -12459,40 +12459,40 @@
       <c r="H41">
         <v>3.48</v>
       </c>
-      <c r="I41" s="511">
+      <c r="I41" s="515">
         <v>6.35</v>
       </c>
-      <c r="J41" s="512">
+      <c r="J41" s="520">
         <v>5.77</v>
       </c>
-      <c r="K41" s="513">
+      <c r="K41" s="508">
         <v>7.88</v>
       </c>
-      <c r="L41" s="517">
+      <c r="L41" s="509">
         <v>2.21</v>
       </c>
-      <c r="M41" s="518">
+      <c r="M41" s="510">
         <v>0.38</v>
       </c>
-      <c r="N41" s="515">
+      <c r="N41" s="511">
         <v>1.44</v>
       </c>
-      <c r="O41" s="508">
+      <c r="O41" s="512">
         <v>1.54</v>
       </c>
-      <c r="P41" s="519">
+      <c r="P41" s="516">
         <v>-0.77</v>
       </c>
-      <c r="Q41" s="520">
+      <c r="Q41" s="517">
         <v>2.98</v>
       </c>
-      <c r="R41" s="509">
+      <c r="R41" s="513">
         <v>4.42</v>
       </c>
       <c r="S41" s="514">
         <v>10.19</v>
       </c>
-      <c r="T41" s="510">
+      <c r="T41" s="518">
         <v>7.02</v>
       </c>
     </row>
@@ -12506,7 +12506,7 @@
       <c r="C42" t="str">
         <v>603629</v>
       </c>
-      <c r="D42" s="532" t="str">
+      <c r="D42" s="523" t="str">
         <v>净卖: -6126.05万</v>
       </c>
       <c r="E42">
@@ -12521,40 +12521,40 @@
       <c r="H42">
         <v>2.1</v>
       </c>
-      <c r="I42" s="530">
+      <c r="I42" s="524">
         <v>-11.86</v>
       </c>
-      <c r="J42" s="526">
+      <c r="J42" s="525">
         <v>-17.19</v>
       </c>
-      <c r="K42" s="527">
+      <c r="K42" s="526">
         <v>-18.01</v>
       </c>
-      <c r="L42" s="533">
+      <c r="L42" s="527">
         <v>-9.81</v>
       </c>
       <c r="M42" s="521">
         <v>-4.96</v>
       </c>
-      <c r="N42" s="522">
+      <c r="N42" s="528">
         <v>-7.22</v>
       </c>
-      <c r="O42" s="528">
+      <c r="O42" s="531">
         <v>-7.38</v>
       </c>
-      <c r="P42" s="523">
+      <c r="P42" s="529">
         <v>-7.57</v>
       </c>
-      <c r="Q42" s="524">
+      <c r="Q42" s="532">
         <v>-5.22</v>
       </c>
-      <c r="R42" s="531">
+      <c r="R42" s="530">
         <v>-13.29</v>
       </c>
-      <c r="S42" s="529">
+      <c r="S42" s="533">
         <v>-14.5</v>
       </c>
-      <c r="T42" s="525">
+      <c r="T42" s="522">
         <v>51.71</v>
       </c>
     </row>
@@ -12568,7 +12568,7 @@
       <c r="C43" t="str">
         <v>002560</v>
       </c>
-      <c r="D43" s="544" t="str">
+      <c r="D43" s="538" t="str">
         <v>净买: 8507.98万</v>
       </c>
       <c r="E43">
@@ -12583,40 +12583,40 @@
       <c r="H43">
         <v>5.38</v>
       </c>
-      <c r="I43" s="534">
+      <c r="I43" s="543">
         <v>4.4</v>
       </c>
-      <c r="J43" s="535">
+      <c r="J43" s="544">
         <v>14.86</v>
       </c>
-      <c r="K43" s="545">
+      <c r="K43" s="537">
         <v>10.99</v>
       </c>
-      <c r="L43" s="542">
+      <c r="L43" s="546">
         <v>16.53</v>
       </c>
-      <c r="M43" s="538">
+      <c r="M43" s="534">
         <v>19.17</v>
       </c>
-      <c r="N43" s="546">
+      <c r="N43" s="539">
         <v>16.71</v>
       </c>
-      <c r="O43" s="539">
+      <c r="O43" s="540">
         <v>19.35</v>
       </c>
-      <c r="P43" s="543">
+      <c r="P43" s="535">
         <v>25.59</v>
       </c>
-      <c r="Q43" s="536">
+      <c r="Q43" s="541">
         <v>21.46</v>
       </c>
-      <c r="R43" s="537">
+      <c r="R43" s="542">
         <v>23.48</v>
       </c>
-      <c r="S43" s="540">
+      <c r="S43" s="536">
         <v>22.34</v>
       </c>
-      <c r="T43" s="541">
+      <c r="T43" s="545">
         <v>22.08</v>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       <c r="C44" t="str">
         <v>002560</v>
       </c>
-      <c r="D44" s="549" t="str">
+      <c r="D44" s="551" t="str">
         <v>净买: 3378.02万</v>
       </c>
       <c r="E44">
@@ -12645,38 +12645,38 @@
       <c r="H44">
         <v>5.51</v>
       </c>
-      <c r="I44" s="555">
+      <c r="I44" s="556">
         <v>-8.42</v>
       </c>
-      <c r="J44" s="556">
+      <c r="J44" s="552">
         <v>-3.85</v>
       </c>
-      <c r="K44" s="547">
+      <c r="K44" s="557">
         <v>-1.67</v>
       </c>
-      <c r="L44" s="550">
+      <c r="L44" s="558">
         <v>-3.7</v>
       </c>
-      <c r="M44" s="551">
+      <c r="M44" s="549">
         <v>-1.52</v>
       </c>
-      <c r="N44" s="548">
+      <c r="N44" s="553">
         <v>3.63</v>
       </c>
-      <c r="O44" s="557">
+      <c r="O44" s="547">
         <v>0.22</v>
       </c>
-      <c r="P44" s="552">
+      <c r="P44" s="554">
         <v>1.89</v>
       </c>
-      <c r="Q44" s="558">
+      <c r="Q44" s="548">
         <v>0.94</v>
       </c>
-      <c r="R44" s="553">
+      <c r="R44" s="555">
         <v>0.73</v>
       </c>
       <c r="S44" t="str"/>
-      <c r="T44" s="554">
+      <c r="T44" s="550">
         <v>0.73</v>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       <c r="C45" t="str">
         <v>603629</v>
       </c>
-      <c r="D45" s="559" t="str">
+      <c r="D45" s="561" t="str">
         <v>净卖: -1.16亿</v>
       </c>
       <c r="E45">
@@ -12705,25 +12705,25 @@
       <c r="H45">
         <v>1.45</v>
       </c>
-      <c r="I45" s="566">
+      <c r="I45" s="564">
         <v>4.48</v>
       </c>
-      <c r="J45" s="564">
+      <c r="J45" s="562">
         <v>1.76</v>
       </c>
-      <c r="K45" s="560">
+      <c r="K45" s="565">
         <v>1.76</v>
       </c>
-      <c r="L45" s="567">
+      <c r="L45" s="559">
         <v>11.94</v>
       </c>
-      <c r="M45" s="565">
+      <c r="M45" s="560">
         <v>23.14</v>
       </c>
-      <c r="N45" s="561">
+      <c r="N45" s="566">
         <v>34.21</v>
       </c>
-      <c r="O45" s="562">
+      <c r="O45" s="567">
         <v>47.63</v>
       </c>
       <c r="P45" t="str"/>
@@ -12959,40 +12959,40 @@
       <c r="F51" t="str"/>
       <c r="G51" t="str"/>
       <c r="H51" t="str"/>
-      <c r="I51" s="586">
+      <c r="I51" s="582">
         <v>68.75</v>
       </c>
-      <c r="J51" s="587">
+      <c r="J51" s="585">
         <v>68.89</v>
       </c>
-      <c r="K51" s="588">
+      <c r="K51" s="579">
         <v>66.67</v>
       </c>
-      <c r="L51" s="579">
+      <c r="L51" s="583">
         <v>59.09</v>
       </c>
-      <c r="M51" s="584">
+      <c r="M51" s="580">
         <v>56.82</v>
       </c>
-      <c r="N51" s="580">
+      <c r="N51" s="586">
         <v>59.09</v>
       </c>
-      <c r="O51" s="585">
+      <c r="O51" s="584">
         <v>61.36</v>
       </c>
-      <c r="P51" s="581">
+      <c r="P51" s="588">
         <v>60.47</v>
       </c>
-      <c r="Q51" s="583">
+      <c r="Q51" s="581">
         <v>60.47</v>
       </c>
-      <c r="R51" s="582">
+      <c r="R51" s="589">
         <v>62.79</v>
       </c>
-      <c r="S51" s="589">
+      <c r="S51" s="590">
         <v>61.9</v>
       </c>
-      <c r="T51" s="590">
+      <c r="T51" s="587">
         <v>60</v>
       </c>
     </row>
@@ -13007,40 +13007,40 @@
       <c r="F52" t="str"/>
       <c r="G52" t="str"/>
       <c r="H52" t="str"/>
-      <c r="I52" s="592">
+      <c r="I52" s="598">
         <v>5.22</v>
       </c>
-      <c r="J52" s="599">
+      <c r="J52" s="601">
         <v>5.43</v>
       </c>
-      <c r="K52" s="595">
+      <c r="K52" s="594">
         <v>5.9</v>
       </c>
-      <c r="L52" s="596">
+      <c r="L52" s="595">
         <v>4.64</v>
       </c>
-      <c r="M52" s="600">
+      <c r="M52" s="602">
         <v>3.87</v>
       </c>
-      <c r="N52" s="601">
+      <c r="N52" s="591">
         <v>4.83</v>
       </c>
-      <c r="O52" s="597">
+      <c r="O52" s="592">
         <v>5.37</v>
       </c>
-      <c r="P52" s="598">
+      <c r="P52" s="596">
         <v>5.02</v>
       </c>
-      <c r="Q52" s="602">
+      <c r="Q52" s="599">
         <v>5.43</v>
       </c>
-      <c r="R52" s="591">
+      <c r="R52" s="593">
         <v>6.06</v>
       </c>
-      <c r="S52" s="593">
+      <c r="S52" s="597">
         <v>7.45</v>
       </c>
-      <c r="T52" s="594">
+      <c r="T52" s="600">
         <v>12.28</v>
       </c>
     </row>

--- a/youzi/屠文斌/index.xlsx
+++ b/youzi/屠文斌/index.xlsx
@@ -45,25 +45,2143 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22923D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56E79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56E79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4DAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,7 +2193,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,7 +2355,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,37 +2391,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,42 +2541,408 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4856"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -195,13 +2961,253 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF29A746"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
+        <fgColor rgb="FF218C3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,37 +3231,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -273,61 +3315,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56C77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D9DC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,49 +3387,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -393,49 +3483,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,169 +3543,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -621,121 +3567,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -765,2887 +3627,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56E79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56E79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4DAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4856"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D9DC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56C77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -10026,7 +10026,7 @@
       <c r="C2" t="str">
         <v>002575</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="7" t="str">
         <v>净买: 1374.90万</v>
       </c>
       <c r="E2">
@@ -10041,40 +10041,40 @@
       <c r="H2">
         <v>-2.88</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="2">
         <v>-7.29</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="3">
         <v>-4.78</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="12">
         <v>-5.92</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="8">
         <v>-6.72</v>
       </c>
       <c r="M2" s="9">
         <v>2.62</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="4">
         <v>1.82</v>
       </c>
       <c r="O2" s="10">
         <v>6.83</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="11">
         <v>17.54</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="13">
         <v>29.27</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="5">
         <v>42.26</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="1">
         <v>47.04</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="6">
         <v>-25.51</v>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       <c r="C3" t="str">
         <v>002575</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -2672.88万</v>
       </c>
       <c r="E3">
@@ -10103,40 +10103,40 @@
       <c r="H3">
         <v>9.98</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="16">
         <v>0</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="24">
         <v>10.04</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="25">
         <v>13.74</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="21">
         <v>2.38</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="26">
         <v>12.6</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="17">
         <v>1.32</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="14">
         <v>-8.28</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="18">
         <v>-6.78</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="23">
         <v>-7.05</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="19">
         <v>-15.42</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="15">
         <v>-13.13</v>
       </c>
-      <c r="T3" s="26">
+      <c r="T3" s="20">
         <v>-42.38</v>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       <c r="C4" t="str">
         <v>605303</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="38" t="str">
         <v>净买: 323.34万</v>
       </c>
       <c r="E4">
@@ -10165,40 +10165,40 @@
       <c r="H4">
         <v>-2.55</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="28">
         <v>-4.97</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="32">
         <v>-5.15</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="36">
         <v>-6.78</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="29">
         <v>-8.31</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="39">
         <v>-9.49</v>
       </c>
       <c r="N4" s="30">
         <v>-10.39</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="31">
         <v>-13.37</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="37">
         <v>-12.74</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="33">
         <v>-14.27</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="34">
         <v>-15.54</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="27">
         <v>-16.71</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="35">
         <v>120.78</v>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       <c r="C5" t="str">
         <v>600590</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="42" t="str">
         <v>净买: 7131.26万</v>
       </c>
       <c r="E5">
@@ -10230,37 +10230,37 @@
       <c r="I5" s="43">
         <v>-8.07</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="52">
         <v>-10.84</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="49">
         <v>-10.84</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="40">
         <v>-15.88</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="50">
         <v>-19.75</v>
       </c>
       <c r="N5" s="48">
         <v>-27.73</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="44">
         <v>-25.21</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="45">
         <v>-17.73</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="46">
         <v>-19.5</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="51">
         <v>-11.43</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="47">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="47">
+      <c r="T5" s="41">
         <v>33.11</v>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       <c r="C6" t="str">
         <v>600063</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="55" t="str">
         <v>净买: 2621.63万</v>
       </c>
       <c r="E6">
@@ -10289,40 +10289,40 @@
       <c r="H6">
         <v>4.82</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="65">
         <v>5.03</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="58">
         <v>0</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="61">
         <v>1.53</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="53">
         <v>2.84</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="54">
         <v>2.63</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="59">
         <v>1.09</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="62">
         <v>0.22</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="60">
         <v>2.84</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="56">
         <v>2.84</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="63">
         <v>1.97</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="64">
         <v>0.88</v>
       </c>
-      <c r="T6" s="62">
+      <c r="T6" s="57">
         <v>53.83</v>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       <c r="C7" t="str">
         <v>002300</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="78" t="str">
         <v>净卖: -2462.36万</v>
       </c>
       <c r="E7">
@@ -10351,40 +10351,40 @@
       <c r="H7">
         <v>0.65</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="70">
         <v>9.34</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="76">
         <v>-0.91</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="77">
         <v>-10.77</v>
       </c>
-      <c r="L7" s="77">
+      <c r="L7" s="71">
         <v>-17.64</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="72">
         <v>-19.97</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="66">
         <v>-20.88</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="73">
         <v>-21.66</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="74">
         <v>-29.44</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="75">
         <v>-31.39</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="67">
         <v>-28.92</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="68">
         <v>-27.63</v>
       </c>
-      <c r="T7" s="67">
+      <c r="T7" s="69">
         <v>22.83</v>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       <c r="C8" t="str">
         <v>605133</v>
       </c>
-      <c r="D8" s="84" t="str">
+      <c r="D8" s="85" t="str">
         <v>净卖: -2062.31万</v>
       </c>
       <c r="E8">
@@ -10413,40 +10413,40 @@
       <c r="H8">
         <v>1.83</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="86">
         <v>7.94</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="81">
         <v>5.89</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="82">
         <v>7.6</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="88">
         <v>8.82</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="87">
         <v>19.7</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="91">
         <v>31.67</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="89">
         <v>32.52</v>
       </c>
-      <c r="P8" s="89">
+      <c r="P8" s="83">
         <v>21.71</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="90">
         <v>26.06</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="79">
         <v>28.27</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="84">
         <v>31.3</v>
       </c>
-      <c r="T8" s="91">
+      <c r="T8" s="80">
         <v>1.86</v>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
       <c r="C9" t="str">
         <v>600187</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="93" t="str">
         <v>净买: 91.44万</v>
       </c>
       <c r="E9">
@@ -10475,40 +10475,40 @@
       <c r="H9">
         <v>-9.97</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="103">
         <v>0</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="98">
         <v>-9.62</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="99">
         <v>-13.12</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="94">
         <v>-14.29</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="100">
         <v>-10.5</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="101">
         <v>-6.12</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="95">
         <v>-6.71</v>
       </c>
       <c r="P9" s="96">
         <v>-6.71</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="104">
         <v>-7.58</v>
       </c>
-      <c r="R9" s="104">
+      <c r="R9" s="102">
         <v>-7</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="97">
         <v>-6.71</v>
       </c>
-      <c r="T9" s="101">
+      <c r="T9" s="92">
         <v>-47.23</v>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       <c r="C10" t="str">
         <v>600439</v>
       </c>
-      <c r="D10" s="117" t="str">
+      <c r="D10" s="107" t="str">
         <v>净买: 1007.14万</v>
       </c>
       <c r="E10">
@@ -10537,40 +10537,40 @@
       <c r="H10">
         <v>-9.46</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="115">
         <v>-0.6</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="110">
         <v>-2.69</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="116">
         <v>-3.58</v>
       </c>
       <c r="L10" s="105">
         <v>-5.97</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="117">
         <v>-5.97</v>
       </c>
       <c r="N10" s="106">
         <v>-5.67</v>
       </c>
-      <c r="O10" s="116">
+      <c r="O10" s="108">
         <v>-5.37</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="111">
         <v>-5.07</v>
       </c>
       <c r="Q10" s="112">
         <v>-5.97</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="109">
         <v>-6.57</v>
       </c>
-      <c r="S10" s="114">
+      <c r="S10" s="113">
         <v>-5.67</v>
       </c>
-      <c r="T10" s="115">
+      <c r="T10" s="114">
         <v>-24.48</v>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       <c r="C11" t="str">
         <v>002611</v>
       </c>
-      <c r="D11" s="122" t="str">
+      <c r="D11" s="127" t="str">
         <v>净买: 2905.14万</v>
       </c>
       <c r="E11">
@@ -10599,37 +10599,37 @@
       <c r="H11">
         <v>0.28</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="130">
         <v>9.68</v>
       </c>
-      <c r="J11" s="130">
+      <c r="J11" s="119">
         <v>20.62</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="120">
         <v>18.58</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="128">
         <v>17.88</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="124">
         <v>20.97</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="121">
         <v>33.1</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="125">
         <v>34.78</v>
       </c>
-      <c r="P11" s="128">
+      <c r="P11" s="118">
         <v>33.38</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="122">
         <v>33.1</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="126">
         <v>35.27</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="123">
         <v>38.15</v>
       </c>
       <c r="T11" s="129">
@@ -10646,7 +10646,7 @@
       <c r="C12" t="str">
         <v>002148</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="138" t="str">
         <v>净卖: -7676.21万</v>
       </c>
       <c r="E12">
@@ -10661,40 +10661,40 @@
       <c r="H12">
         <v>8.07</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="141">
         <v>1.78</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="142">
         <v>12</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="131">
         <v>14.13</v>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="132">
         <v>18.67</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="133">
         <v>24.62</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="143">
         <v>12.53</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="139">
         <v>11.82</v>
       </c>
-      <c r="P12" s="132">
+      <c r="P12" s="134">
         <v>10.04</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="135">
         <v>5.42</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="136">
         <v>4</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="137">
         <v>2.31</v>
       </c>
-      <c r="T12" s="134">
+      <c r="T12" s="140">
         <v>-30.76</v>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       <c r="C13" t="str">
         <v>002148</v>
       </c>
-      <c r="D13" s="155" t="str">
+      <c r="D13" s="154" t="str">
         <v>净卖: -7781.22万</v>
       </c>
       <c r="E13">
@@ -10723,40 +10723,40 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="155">
         <v>10.04</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="152">
         <v>12.14</v>
       </c>
-      <c r="K13" s="156">
+      <c r="K13" s="147">
         <v>16.59</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="148">
         <v>22.45</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="156">
         <v>10.57</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="149">
         <v>9.87</v>
       </c>
       <c r="O13" s="151">
         <v>8.12</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="150">
         <v>3.58</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="144">
         <v>2.18</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="145">
         <v>0.52</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="153">
         <v>0.61</v>
       </c>
-      <c r="T13" s="154">
+      <c r="T13" s="146">
         <v>-31.97</v>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       <c r="C14" t="str">
         <v>000700</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="161" t="str">
         <v>净买: 6133.53万</v>
       </c>
       <c r="E14">
@@ -10785,40 +10785,40 @@
       <c r="H14">
         <v>3.92</v>
       </c>
-      <c r="I14" s="159">
+      <c r="I14" s="164">
         <v>5.83</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="158">
         <v>4.1</v>
       </c>
-      <c r="K14" s="165">
+      <c r="K14" s="159">
         <v>1.94</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="162">
         <v>2.05</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="160">
         <v>12.3</v>
       </c>
-      <c r="N14" s="162">
+      <c r="N14" s="165">
         <v>2.91</v>
       </c>
-      <c r="O14" s="167">
+      <c r="O14" s="166">
         <v>5.61</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="167">
         <v>3.67</v>
       </c>
       <c r="Q14" s="168">
         <v>4.31</v>
       </c>
-      <c r="R14" s="169">
+      <c r="R14" s="163">
         <v>5.18</v>
       </c>
-      <c r="S14" s="157">
+      <c r="S14" s="169">
         <v>6.26</v>
       </c>
-      <c r="T14" s="158">
+      <c r="T14" s="157">
         <v>26.54</v>
       </c>
     </row>
@@ -10832,7 +10832,7 @@
       <c r="C15" t="str">
         <v>603222</v>
       </c>
-      <c r="D15" s="176" t="str">
+      <c r="D15" s="178" t="str">
         <v>净买: 2341.28万</v>
       </c>
       <c r="E15">
@@ -10847,40 +10847,40 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="176">
         <v>0</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="181">
         <v>10.02</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="170">
         <v>5.75</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="177">
         <v>-4.82</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="179">
         <v>-8.26</v>
       </c>
       <c r="N15" s="180">
         <v>-15.31</v>
       </c>
-      <c r="O15" s="182">
+      <c r="O15" s="171">
         <v>-6.86</v>
       </c>
-      <c r="P15" s="170">
+      <c r="P15" s="182">
         <v>2.41</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="172">
         <v>6.86</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="173">
         <v>17.53</v>
       </c>
-      <c r="S15" s="171">
+      <c r="S15" s="174">
         <v>5.75</v>
       </c>
-      <c r="T15" s="174">
+      <c r="T15" s="175">
         <v>-2.23</v>
       </c>
     </row>
@@ -10894,7 +10894,7 @@
       <c r="C16" t="str">
         <v>603222</v>
       </c>
-      <c r="D16" s="186" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 2384.77万</v>
       </c>
       <c r="E16">
@@ -10912,25 +10912,25 @@
       <c r="I16" s="187">
         <v>-7.57</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="184">
         <v>-10.9</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="188">
         <v>-17.75</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="191">
         <v>-9.55</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="192">
         <v>-0.54</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="185">
         <v>3.78</v>
       </c>
-      <c r="O16" s="189">
+      <c r="O16" s="186">
         <v>14.14</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="193">
         <v>2.7</v>
       </c>
       <c r="Q16" s="194">
@@ -10939,10 +10939,10 @@
       <c r="R16" s="195">
         <v>3.78</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="189">
         <v>-5.32</v>
       </c>
-      <c r="T16" s="185">
+      <c r="T16" s="183">
         <v>-5.05</v>
       </c>
     </row>
@@ -10956,7 +10956,7 @@
       <c r="C17" t="str">
         <v>603222</v>
       </c>
-      <c r="D17" s="208" t="str">
+      <c r="D17" s="197" t="str">
         <v>净卖: -1529.63万</v>
       </c>
       <c r="E17">
@@ -10971,40 +10971,40 @@
       <c r="H17">
         <v>-3.39</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="198">
         <v>13.81</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="202">
         <v>18.76</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="199">
         <v>30.62</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="205">
         <v>17.53</v>
       </c>
-      <c r="M17" s="197">
+      <c r="M17" s="200">
         <v>7.94</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="201">
         <v>18.76</v>
       </c>
       <c r="O17" s="203">
         <v>8.35</v>
       </c>
-      <c r="P17" s="207">
+      <c r="P17" s="204">
         <v>19.18</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="196">
         <v>29.38</v>
       </c>
-      <c r="R17" s="204">
+      <c r="R17" s="206">
         <v>31.75</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="207">
         <v>44.95</v>
       </c>
-      <c r="T17" s="200">
+      <c r="T17" s="208">
         <v>8.66</v>
       </c>
     </row>
@@ -11018,7 +11018,7 @@
       <c r="C18" t="str">
         <v>600330</v>
       </c>
-      <c r="D18" s="220" t="str">
+      <c r="D18" s="213" t="str">
         <v>净卖: -5410.71万</v>
       </c>
       <c r="E18">
@@ -11033,40 +11033,40 @@
       <c r="H18">
         <v>10</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="214">
         <v>-5.66</v>
       </c>
-      <c r="J18" s="218">
+      <c r="J18" s="215">
         <v>3.77</v>
       </c>
-      <c r="K18" s="214">
+      <c r="K18" s="210">
         <v>-0.51</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="217">
         <v>-7.72</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="221">
         <v>-10.89</v>
       </c>
-      <c r="N18" s="215">
+      <c r="N18" s="218">
         <v>-6.43</v>
       </c>
-      <c r="O18" s="209">
+      <c r="O18" s="211">
         <v>-8.23</v>
       </c>
-      <c r="P18" s="216">
+      <c r="P18" s="212">
         <v>-3.77</v>
       </c>
-      <c r="Q18" s="210">
+      <c r="Q18" s="219">
         <v>-2.23</v>
       </c>
-      <c r="R18" s="217">
+      <c r="R18" s="209">
         <v>-1.63</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="220">
         <v>-0.77</v>
       </c>
-      <c r="T18" s="213">
+      <c r="T18" s="216">
         <v>86.36</v>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       <c r="C19" t="str">
         <v>688593</v>
       </c>
-      <c r="D19" s="234" t="str">
+      <c r="D19" s="225" t="str">
         <v>净买: 1943.52万</v>
       </c>
       <c r="E19">
@@ -11095,40 +11095,40 @@
       <c r="H19">
         <v>-0.06</v>
       </c>
-      <c r="I19" s="230">
+      <c r="I19" s="231">
         <v>20.07</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="229">
         <v>35.34</v>
       </c>
-      <c r="K19" s="228">
+      <c r="K19" s="232">
         <v>35.22</v>
       </c>
-      <c r="L19" s="229">
+      <c r="L19" s="230">
         <v>46.33</v>
       </c>
-      <c r="M19" s="223">
+      <c r="M19" s="222">
         <v>43.45</v>
       </c>
-      <c r="N19" s="231">
+      <c r="N19" s="233">
         <v>51.86</v>
       </c>
-      <c r="O19" s="224">
+      <c r="O19" s="226">
         <v>52.76</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="234">
         <v>39.24</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="227">
         <v>39.12</v>
       </c>
-      <c r="R19" s="233">
+      <c r="R19" s="228">
         <v>39.48</v>
       </c>
-      <c r="S19" s="226">
+      <c r="S19" s="223">
         <v>35.58</v>
       </c>
-      <c r="T19" s="227">
+      <c r="T19" s="224">
         <v>86.72</v>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       <c r="C20" t="str">
         <v>605398</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="236" t="str">
         <v>净买: 2437.63万</v>
       </c>
       <c r="E20">
@@ -11157,40 +11157,40 @@
       <c r="H20">
         <v>9.99</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="246">
         <v>0</v>
       </c>
-      <c r="J20" s="240">
+      <c r="J20" s="237">
         <v>-10</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="238">
         <v>-11.75</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="239">
         <v>-15.79</v>
       </c>
       <c r="M20" s="247">
         <v>-17.23</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="240">
         <v>-18.88</v>
       </c>
-      <c r="O20" s="246">
+      <c r="O20" s="243">
         <v>-19.34</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="241">
         <v>-20.05</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="244">
         <v>-18.83</v>
       </c>
-      <c r="R20" s="243">
+      <c r="R20" s="242">
         <v>-19.44</v>
       </c>
       <c r="S20" s="235">
         <v>-21.88</v>
       </c>
-      <c r="T20" s="236">
+      <c r="T20" s="245">
         <v>-30.33</v>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
       <c r="C21" t="str">
         <v>000988</v>
       </c>
-      <c r="D21" s="248" t="str">
+      <c r="D21" s="251" t="str">
         <v>净买: 3.56亿</v>
       </c>
       <c r="E21">
@@ -11222,37 +11222,37 @@
       <c r="I21" s="252">
         <v>3.48</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="259">
         <v>3.58</v>
       </c>
       <c r="K21" s="253">
         <v>8.96</v>
       </c>
-      <c r="L21" s="254">
+      <c r="L21" s="260">
         <v>11.51</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="254">
         <v>16.03</v>
       </c>
-      <c r="N21" s="250">
+      <c r="N21" s="248">
         <v>17.6</v>
       </c>
-      <c r="O21" s="260">
+      <c r="O21" s="249">
         <v>12.38</v>
       </c>
-      <c r="P21" s="258">
+      <c r="P21" s="255">
         <v>13.08</v>
       </c>
-      <c r="Q21" s="259">
+      <c r="Q21" s="250">
         <v>24.39</v>
       </c>
-      <c r="R21" s="251">
+      <c r="R21" s="256">
         <v>17.41</v>
       </c>
-      <c r="S21" s="255">
+      <c r="S21" s="257">
         <v>26.26</v>
       </c>
-      <c r="T21" s="256">
+      <c r="T21" s="258">
         <v>48.58</v>
       </c>
     </row>
@@ -11266,7 +11266,7 @@
       <c r="C22" t="str">
         <v>300507</v>
       </c>
-      <c r="D22" s="271" t="str">
+      <c r="D22" s="269" t="str">
         <v>净买: 6982.34万</v>
       </c>
       <c r="E22">
@@ -11281,40 +11281,40 @@
       <c r="H22">
         <v>0.23</v>
       </c>
-      <c r="I22" s="267">
+      <c r="I22" s="262">
         <v>19.72</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="270">
         <v>17.09</v>
       </c>
-      <c r="K22" s="273">
+      <c r="K22" s="271">
         <v>15.6</v>
       </c>
-      <c r="L22" s="261">
+      <c r="L22" s="267">
         <v>16.28</v>
       </c>
-      <c r="M22" s="270">
+      <c r="M22" s="263">
         <v>17.32</v>
       </c>
       <c r="N22" s="264">
         <v>12.39</v>
       </c>
-      <c r="O22" s="262">
+      <c r="O22" s="265">
         <v>11.24</v>
       </c>
-      <c r="P22" s="265">
+      <c r="P22" s="268">
         <v>8.94</v>
       </c>
-      <c r="Q22" s="266">
+      <c r="Q22" s="272">
         <v>7.57</v>
       </c>
-      <c r="R22" s="268">
+      <c r="R22" s="273">
         <v>18.35</v>
       </c>
-      <c r="S22" s="269">
+      <c r="S22" s="266">
         <v>15.94</v>
       </c>
-      <c r="T22" s="263">
+      <c r="T22" s="261">
         <v>1.61</v>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       <c r="C23" t="str">
         <v>000988</v>
       </c>
-      <c r="D23" s="275" t="str">
+      <c r="D23" s="286" t="str">
         <v>净买: 1.74亿</v>
       </c>
       <c r="E23">
@@ -11343,40 +11343,40 @@
       <c r="H23">
         <v>2.59</v>
       </c>
-      <c r="I23" s="276">
+      <c r="I23" s="281">
         <v>7.22</v>
       </c>
-      <c r="J23" s="284">
+      <c r="J23" s="282">
         <v>1.21</v>
       </c>
-      <c r="K23" s="282">
+      <c r="K23" s="274">
         <v>8.84</v>
       </c>
       <c r="L23" s="277">
         <v>1.51</v>
       </c>
-      <c r="M23" s="285">
+      <c r="M23" s="283">
         <v>-2.95</v>
       </c>
-      <c r="N23" s="286">
+      <c r="N23" s="278">
         <v>-6.43</v>
       </c>
-      <c r="O23" s="278">
+      <c r="O23" s="279">
         <v>-9.42</v>
       </c>
-      <c r="P23" s="279">
+      <c r="P23" s="284">
         <v>-13.77</v>
       </c>
-      <c r="Q23" s="283">
+      <c r="Q23" s="280">
         <v>-11.78</v>
       </c>
-      <c r="R23" s="280">
+      <c r="R23" s="275">
         <v>-11.13</v>
       </c>
-      <c r="S23" s="274">
+      <c r="S23" s="285">
         <v>-14.93</v>
       </c>
-      <c r="T23" s="281">
+      <c r="T23" s="276">
         <v>28.08</v>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       <c r="C24" t="str">
         <v>300948</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="297" t="str">
         <v>净卖: -57.39万</v>
       </c>
       <c r="E24">
@@ -11405,40 +11405,40 @@
       <c r="H24">
         <v>20</v>
       </c>
-      <c r="I24" s="291">
+      <c r="I24" s="287">
         <v>0</v>
       </c>
-      <c r="J24" s="297">
+      <c r="J24" s="288">
         <v>20.01</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="298">
         <v>44.05</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="294">
         <v>63.39</v>
       </c>
-      <c r="M24" s="299">
+      <c r="M24" s="290">
         <v>37.5</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="295">
         <v>46.5</v>
       </c>
-      <c r="O24" s="294">
+      <c r="O24" s="296">
         <v>45.24</v>
       </c>
-      <c r="P24" s="287">
+      <c r="P24" s="291">
         <v>49.55</v>
       </c>
-      <c r="Q24" s="295">
+      <c r="Q24" s="292">
         <v>42.04</v>
       </c>
-      <c r="R24" s="296">
+      <c r="R24" s="299">
         <v>36.61</v>
       </c>
-      <c r="S24" s="289">
+      <c r="S24" s="293">
         <v>63.91</v>
       </c>
-      <c r="T24" s="290">
+      <c r="T24" s="289">
         <v>43.6</v>
       </c>
     </row>
@@ -11467,40 +11467,40 @@
       <c r="H25">
         <v>1.05</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="302">
         <v>-7.7</v>
       </c>
-      <c r="J25" s="311">
+      <c r="J25" s="303">
         <v>-11.76</v>
       </c>
-      <c r="K25" s="312">
+      <c r="K25" s="311">
         <v>-14.92</v>
       </c>
-      <c r="L25" s="305">
+      <c r="L25" s="306">
         <v>-17.64</v>
       </c>
-      <c r="M25" s="306">
+      <c r="M25" s="304">
         <v>-21.59</v>
       </c>
-      <c r="N25" s="300">
+      <c r="N25" s="312">
         <v>-19.78</v>
       </c>
-      <c r="O25" s="307">
+      <c r="O25" s="309">
         <v>-19.19</v>
       </c>
-      <c r="P25" s="309">
+      <c r="P25" s="307">
         <v>-22.65</v>
       </c>
-      <c r="Q25" s="302">
+      <c r="Q25" s="300">
         <v>-20.41</v>
       </c>
-      <c r="R25" s="310">
+      <c r="R25" s="305">
         <v>-17.38</v>
       </c>
-      <c r="S25" s="303">
+      <c r="S25" s="308">
         <v>-15</v>
       </c>
-      <c r="T25" s="304">
+      <c r="T25" s="310">
         <v>16.46</v>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       <c r="C26" t="str">
         <v>600067</v>
       </c>
-      <c r="D26" s="322" t="str">
+      <c r="D26" s="313" t="str">
         <v>净买: 785.29万</v>
       </c>
       <c r="E26">
@@ -11529,40 +11529,40 @@
       <c r="H26">
         <v>4.48</v>
       </c>
-      <c r="I26" s="320">
+      <c r="I26" s="314">
         <v>5.36</v>
       </c>
-      <c r="J26" s="314">
+      <c r="J26" s="315">
         <v>8.85</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="319">
         <v>19.84</v>
       </c>
-      <c r="L26" s="315">
+      <c r="L26" s="320">
         <v>19.3</v>
       </c>
-      <c r="M26" s="323">
+      <c r="M26" s="317">
         <v>10.19</v>
       </c>
-      <c r="N26" s="317">
+      <c r="N26" s="323">
         <v>11.53</v>
       </c>
       <c r="O26" s="318">
         <v>22.79</v>
       </c>
-      <c r="P26" s="324">
+      <c r="P26" s="316">
         <v>28.42</v>
       </c>
-      <c r="Q26" s="325">
+      <c r="Q26" s="324">
         <v>26.01</v>
       </c>
-      <c r="R26" s="313">
+      <c r="R26" s="325">
         <v>30.56</v>
       </c>
-      <c r="S26" s="319">
+      <c r="S26" s="321">
         <v>35.66</v>
       </c>
-      <c r="T26" s="316">
+      <c r="T26" s="322">
         <v>10.72</v>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       <c r="C27" t="str">
         <v>300102</v>
       </c>
-      <c r="D27" s="335" t="str">
+      <c r="D27" s="329" t="str">
         <v>净买: 5184.05万</v>
       </c>
       <c r="E27">
@@ -11591,40 +11591,40 @@
       <c r="H27">
         <v>13.28</v>
       </c>
-      <c r="I27" s="333">
+      <c r="I27" s="334">
         <v>5.94</v>
       </c>
-      <c r="J27" s="327">
+      <c r="J27" s="326">
         <v>16.67</v>
       </c>
-      <c r="K27" s="329">
+      <c r="K27" s="330">
         <v>22.39</v>
       </c>
-      <c r="L27" s="330">
+      <c r="L27" s="331">
         <v>10.78</v>
       </c>
-      <c r="M27" s="336">
+      <c r="M27" s="327">
         <v>16.44</v>
       </c>
-      <c r="N27" s="337">
+      <c r="N27" s="332">
         <v>32.67</v>
       </c>
-      <c r="O27" s="338">
+      <c r="O27" s="328">
         <v>31.06</v>
       </c>
-      <c r="P27" s="331">
+      <c r="P27" s="333">
         <v>46</v>
       </c>
-      <c r="Q27" s="326">
+      <c r="Q27" s="335">
         <v>44</v>
       </c>
-      <c r="R27" s="332">
+      <c r="R27" s="336">
         <v>41.67</v>
       </c>
-      <c r="S27" s="328">
+      <c r="S27" s="338">
         <v>46.22</v>
       </c>
-      <c r="T27" s="334">
+      <c r="T27" s="337">
         <v>82.78</v>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
       <c r="C28" t="str">
         <v>688239</v>
       </c>
-      <c r="D28" s="345" t="str">
+      <c r="D28" s="342" t="str">
         <v>净买: 1.73亿</v>
       </c>
       <c r="E28">
@@ -11653,40 +11653,40 @@
       <c r="H28">
         <v>0.62</v>
       </c>
-      <c r="I28" s="340">
+      <c r="I28" s="341">
         <v>19.11</v>
       </c>
-      <c r="J28" s="346">
+      <c r="J28" s="343">
         <v>13.38</v>
       </c>
       <c r="K28" s="347">
         <v>10.24</v>
       </c>
-      <c r="L28" s="341">
+      <c r="L28" s="344">
         <v>10.39</v>
       </c>
-      <c r="M28" s="348">
+      <c r="M28" s="345">
         <v>6.52</v>
       </c>
-      <c r="N28" s="349">
+      <c r="N28" s="351">
         <v>7.9</v>
       </c>
-      <c r="O28" s="342">
+      <c r="O28" s="348">
         <v>7.76</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="349">
         <v>4.43</v>
       </c>
-      <c r="Q28" s="351">
+      <c r="Q28" s="350">
         <v>9.54</v>
       </c>
       <c r="R28" s="339">
         <v>11.84</v>
       </c>
-      <c r="S28" s="343">
+      <c r="S28" s="340">
         <v>15.56</v>
       </c>
-      <c r="T28" s="344">
+      <c r="T28" s="346">
         <v>11.18</v>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       <c r="C29" t="str">
         <v>605007</v>
       </c>
-      <c r="D29" s="359" t="str">
+      <c r="D29" s="356" t="str">
         <v>净买: 863.46万</v>
       </c>
       <c r="E29">
@@ -11715,40 +11715,40 @@
       <c r="H29">
         <v>6.98</v>
       </c>
-      <c r="I29" s="354">
+      <c r="I29" s="357">
         <v>2.83</v>
       </c>
-      <c r="J29" s="355">
+      <c r="J29" s="358">
         <v>13.12</v>
       </c>
-      <c r="K29" s="360">
+      <c r="K29" s="359">
         <v>1.81</v>
       </c>
-      <c r="L29" s="364">
+      <c r="L29" s="352">
         <v>-0.51</v>
       </c>
-      <c r="M29" s="352">
+      <c r="M29" s="353">
         <v>-2.1</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="360">
         <v>-1.88</v>
       </c>
-      <c r="O29" s="353">
+      <c r="O29" s="362">
         <v>-1.59</v>
       </c>
       <c r="P29" s="363">
         <v>-3.91</v>
       </c>
-      <c r="Q29" s="357">
+      <c r="Q29" s="355">
         <v>-3.41</v>
       </c>
       <c r="R29" s="361">
         <v>-2.46</v>
       </c>
-      <c r="S29" s="358">
+      <c r="S29" s="354">
         <v>-1.96</v>
       </c>
-      <c r="T29" s="362">
+      <c r="T29" s="364">
         <v>5.43</v>
       </c>
     </row>
@@ -11762,7 +11762,7 @@
       <c r="C30" t="str">
         <v>300102</v>
       </c>
-      <c r="D30" s="374" t="str">
+      <c r="D30" s="373" t="str">
         <v>净卖: -1.54亿</v>
       </c>
       <c r="E30">
@@ -11777,40 +11777,40 @@
       <c r="H30">
         <v>8.69</v>
       </c>
-      <c r="I30" s="375">
+      <c r="I30" s="369">
         <v>10.41</v>
       </c>
-      <c r="J30" s="368">
+      <c r="J30" s="366">
         <v>14.72</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="370">
         <v>5.96</v>
       </c>
-      <c r="L30" s="369">
+      <c r="L30" s="374">
         <v>2.21</v>
       </c>
-      <c r="M30" s="377">
+      <c r="M30" s="375">
         <v>-3.33</v>
       </c>
-      <c r="N30" s="365">
+      <c r="N30" s="371">
         <v>-2.48</v>
       </c>
-      <c r="O30" s="372">
+      <c r="O30" s="376">
         <v>0.97</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="367">
         <v>-6.08</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="368">
         <v>-8.26</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="377">
         <v>-3.72</v>
       </c>
-      <c r="S30" s="367">
+      <c r="S30" s="365">
         <v>15.55</v>
       </c>
-      <c r="T30" s="373">
+      <c r="T30" s="372">
         <v>-2.95</v>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       <c r="C31" t="str">
         <v>300830</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="386" t="str">
         <v>净买: 5772.47万</v>
       </c>
       <c r="E31">
@@ -11839,40 +11839,40 @@
       <c r="H31">
         <v>7.44</v>
       </c>
-      <c r="I31" s="386">
+      <c r="I31" s="381">
         <v>11.69</v>
       </c>
-      <c r="J31" s="378">
+      <c r="J31" s="387">
         <v>5.08</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="382">
         <v>7.69</v>
       </c>
-      <c r="L31" s="387">
+      <c r="L31" s="383">
         <v>-1.38</v>
       </c>
       <c r="M31" s="388">
         <v>-5.85</v>
       </c>
-      <c r="N31" s="389">
+      <c r="N31" s="384">
         <v>-4.77</v>
       </c>
-      <c r="O31" s="380">
+      <c r="O31" s="389">
         <v>-0.92</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="390">
         <v>7.31</v>
       </c>
-      <c r="Q31" s="382">
+      <c r="Q31" s="378">
         <v>8.38</v>
       </c>
-      <c r="R31" s="383">
+      <c r="R31" s="379">
         <v>13.62</v>
       </c>
-      <c r="S31" s="384">
+      <c r="S31" s="380">
         <v>17.38</v>
       </c>
-      <c r="T31" s="390">
+      <c r="T31" s="385">
         <v>-15.85</v>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       <c r="C32" t="str">
         <v>002181</v>
       </c>
-      <c r="D32" s="401" t="str">
+      <c r="D32" s="391" t="str">
         <v>净买: 3260.12万</v>
       </c>
       <c r="E32">
@@ -11901,40 +11901,40 @@
       <c r="H32">
         <v>2.98</v>
       </c>
-      <c r="I32" s="396">
+      <c r="I32" s="392">
         <v>6.84</v>
       </c>
-      <c r="J32" s="393">
+      <c r="J32" s="396">
         <v>1.16</v>
       </c>
-      <c r="K32" s="402">
+      <c r="K32" s="399">
         <v>11.27</v>
       </c>
-      <c r="L32" s="397">
+      <c r="L32" s="400">
         <v>5.49</v>
       </c>
-      <c r="M32" s="398">
+      <c r="M32" s="393">
         <v>2.22</v>
       </c>
-      <c r="N32" s="403">
+      <c r="N32" s="401">
         <v>-2.02</v>
       </c>
-      <c r="O32" s="391">
+      <c r="O32" s="397">
         <v>7.8</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="398">
         <v>11.85</v>
       </c>
-      <c r="Q32" s="394">
+      <c r="Q32" s="402">
         <v>16.28</v>
       </c>
-      <c r="R32" s="395">
+      <c r="R32" s="394">
         <v>12.52</v>
       </c>
-      <c r="S32" s="399">
+      <c r="S32" s="395">
         <v>13.1</v>
       </c>
-      <c r="T32" s="400">
+      <c r="T32" s="403">
         <v>32.08</v>
       </c>
     </row>
@@ -11948,7 +11948,7 @@
       <c r="C33" t="str">
         <v>300229</v>
       </c>
-      <c r="D33" s="416" t="str">
+      <c r="D33" s="408" t="str">
         <v>净买: 1.91亿</v>
       </c>
       <c r="E33">
@@ -11963,40 +11963,40 @@
       <c r="H33">
         <v>-2.13</v>
       </c>
-      <c r="I33" s="410">
+      <c r="I33" s="413">
         <v>17.73</v>
       </c>
-      <c r="J33" s="413">
+      <c r="J33" s="416">
         <v>3.16</v>
       </c>
       <c r="K33" s="404">
         <v>-4.16</v>
       </c>
-      <c r="L33" s="411">
+      <c r="L33" s="414">
         <v>-6.48</v>
       </c>
-      <c r="M33" s="405">
+      <c r="M33" s="409">
         <v>-8.77</v>
       </c>
-      <c r="N33" s="406">
+      <c r="N33" s="410">
         <v>-9.65</v>
       </c>
-      <c r="O33" s="407">
+      <c r="O33" s="405">
         <v>-8.58</v>
       </c>
-      <c r="P33" s="408">
+      <c r="P33" s="415">
         <v>-6.37</v>
       </c>
-      <c r="Q33" s="409">
+      <c r="Q33" s="406">
         <v>-9.15</v>
       </c>
-      <c r="R33" s="412">
+      <c r="R33" s="407">
         <v>-7.43</v>
       </c>
-      <c r="S33" s="414">
+      <c r="S33" s="411">
         <v>-11.25</v>
       </c>
-      <c r="T33" s="415">
+      <c r="T33" s="412">
         <v>-28.67</v>
       </c>
     </row>
@@ -12010,7 +12010,7 @@
       <c r="C34" t="str">
         <v>603311</v>
       </c>
-      <c r="D34" s="426" t="str">
+      <c r="D34" s="417" t="str">
         <v>净卖: -911.79万</v>
       </c>
       <c r="E34">
@@ -12025,40 +12025,40 @@
       <c r="H34">
         <v>0.6</v>
       </c>
-      <c r="I34" s="421">
+      <c r="I34" s="422">
         <v>9.37</v>
       </c>
-      <c r="J34" s="422">
+      <c r="J34" s="418">
         <v>8.11</v>
       </c>
-      <c r="K34" s="427">
+      <c r="K34" s="426">
         <v>5.58</v>
       </c>
-      <c r="L34" s="425">
+      <c r="L34" s="429">
         <v>5.91</v>
       </c>
-      <c r="M34" s="417">
+      <c r="M34" s="419">
         <v>5.65</v>
       </c>
-      <c r="N34" s="428">
+      <c r="N34" s="427">
         <v>3.46</v>
       </c>
-      <c r="O34" s="423">
+      <c r="O34" s="420">
         <v>8.04</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="423">
         <v>7.84</v>
       </c>
-      <c r="Q34" s="419">
+      <c r="Q34" s="428">
         <v>6.51</v>
       </c>
-      <c r="R34" s="420">
+      <c r="R34" s="421">
         <v>6.51</v>
       </c>
       <c r="S34" s="424">
         <v>4.52</v>
       </c>
-      <c r="T34" s="429">
+      <c r="T34" s="425">
         <v>32.23</v>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
       <c r="C35" t="str">
         <v>002279</v>
       </c>
-      <c r="D35" s="434" t="str">
+      <c r="D35" s="441" t="str">
         <v>净买: 4355.47万</v>
       </c>
       <c r="E35">
@@ -12087,40 +12087,40 @@
       <c r="H35">
         <v>3.46</v>
       </c>
-      <c r="I35" s="440">
+      <c r="I35" s="442">
         <v>6.29</v>
       </c>
-      <c r="J35" s="435">
+      <c r="J35" s="430">
         <v>4.36</v>
       </c>
-      <c r="K35" s="436">
+      <c r="K35" s="439">
         <v>2.43</v>
       </c>
-      <c r="L35" s="441">
+      <c r="L35" s="435">
         <v>9.74</v>
       </c>
-      <c r="M35" s="442">
+      <c r="M35" s="431">
         <v>4.77</v>
       </c>
-      <c r="N35" s="437">
+      <c r="N35" s="436">
         <v>8.01</v>
       </c>
-      <c r="O35" s="438">
+      <c r="O35" s="432">
         <v>3.85</v>
       </c>
-      <c r="P35" s="430">
+      <c r="P35" s="437">
         <v>2.03</v>
       </c>
-      <c r="Q35" s="431">
+      <c r="Q35" s="438">
         <v>5.78</v>
       </c>
-      <c r="R35" s="439">
+      <c r="R35" s="433">
         <v>1.93</v>
       </c>
-      <c r="S35" s="432">
+      <c r="S35" s="434">
         <v>0.61</v>
       </c>
-      <c r="T35" s="433">
+      <c r="T35" s="440">
         <v>-17.04</v>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       <c r="C36" t="str">
         <v>002115</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="454" t="str">
         <v>净卖: -7662.33万</v>
       </c>
       <c r="E36">
@@ -12149,40 +12149,40 @@
       <c r="H36">
         <v>1.82</v>
       </c>
-      <c r="I36" s="444">
+      <c r="I36" s="455">
         <v>5.92</v>
       </c>
-      <c r="J36" s="454">
+      <c r="J36" s="451">
         <v>-1.58</v>
       </c>
-      <c r="K36" s="448">
+      <c r="K36" s="443">
         <v>8.26</v>
       </c>
-      <c r="L36" s="449">
+      <c r="L36" s="452">
         <v>6.06</v>
       </c>
-      <c r="M36" s="445">
+      <c r="M36" s="448">
         <v>8.05</v>
       </c>
-      <c r="N36" s="450">
+      <c r="N36" s="444">
         <v>2.75</v>
       </c>
-      <c r="O36" s="446">
+      <c r="O36" s="445">
         <v>0.48</v>
       </c>
-      <c r="P36" s="451">
+      <c r="P36" s="449">
         <v>7.02</v>
       </c>
-      <c r="Q36" s="455">
+      <c r="Q36" s="450">
         <v>5.3</v>
       </c>
-      <c r="R36" s="452">
+      <c r="R36" s="447">
         <v>3.44</v>
       </c>
-      <c r="S36" s="443">
+      <c r="S36" s="446">
         <v>0.34</v>
       </c>
-      <c r="T36" s="447">
+      <c r="T36" s="453">
         <v>-13.49</v>
       </c>
     </row>
@@ -12211,16 +12211,16 @@
       <c r="H37">
         <v>-4.19</v>
       </c>
-      <c r="I37" s="467">
+      <c r="I37" s="456">
         <v>25.24</v>
       </c>
-      <c r="J37" s="468">
+      <c r="J37" s="466">
         <v>19.99</v>
       </c>
       <c r="K37" s="463">
         <v>21.66</v>
       </c>
-      <c r="L37" s="456">
+      <c r="L37" s="467">
         <v>29.47</v>
       </c>
       <c r="M37" s="464">
@@ -12232,19 +12232,19 @@
       <c r="O37" s="460">
         <v>10.5</v>
       </c>
-      <c r="P37" s="461">
+      <c r="P37" s="465">
         <v>19.99</v>
       </c>
-      <c r="Q37" s="458">
+      <c r="Q37" s="461">
         <v>15.68</v>
       </c>
-      <c r="R37" s="459">
+      <c r="R37" s="458">
         <v>10.14</v>
       </c>
-      <c r="S37" s="465">
+      <c r="S37" s="459">
         <v>8.97</v>
       </c>
-      <c r="T37" s="466">
+      <c r="T37" s="468">
         <v>-10.87</v>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       <c r="C38" t="str">
         <v>300063</v>
       </c>
-      <c r="D38" s="469" t="str">
+      <c r="D38" s="481" t="str">
         <v>净卖: -4187.17万</v>
       </c>
       <c r="E38">
@@ -12273,16 +12273,16 @@
       <c r="H38">
         <v>0.73</v>
       </c>
-      <c r="I38" s="478">
+      <c r="I38" s="475">
         <v>0.66</v>
       </c>
-      <c r="J38" s="470">
+      <c r="J38" s="469">
         <v>7.12</v>
       </c>
-      <c r="K38" s="471">
+      <c r="K38" s="473">
         <v>-1.45</v>
       </c>
-      <c r="L38" s="472">
+      <c r="L38" s="476">
         <v>-6.34</v>
       </c>
       <c r="M38" s="479">
@@ -12291,22 +12291,22 @@
       <c r="N38" s="480">
         <v>-0.72</v>
       </c>
-      <c r="O38" s="473">
+      <c r="O38" s="470">
         <v>-4.28</v>
       </c>
       <c r="P38" s="474">
         <v>-8.87</v>
       </c>
-      <c r="Q38" s="476">
+      <c r="Q38" s="471">
         <v>-9.84</v>
       </c>
-      <c r="R38" s="475">
+      <c r="R38" s="477">
         <v>-13.88</v>
       </c>
-      <c r="S38" s="481">
+      <c r="S38" s="472">
         <v>-14.67</v>
       </c>
-      <c r="T38" s="477">
+      <c r="T38" s="478">
         <v>-26.25</v>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
       <c r="C39" t="str">
         <v>603103</v>
       </c>
-      <c r="D39" s="493" t="str">
+      <c r="D39" s="489" t="str">
         <v>净买: 513.73万</v>
       </c>
       <c r="E39">
@@ -12335,40 +12335,40 @@
       <c r="H39">
         <v>-10</v>
       </c>
-      <c r="I39" s="494">
+      <c r="I39" s="484">
         <v>0</v>
       </c>
       <c r="J39" s="482">
         <v>-6.9</v>
       </c>
-      <c r="K39" s="487">
+      <c r="K39" s="483">
         <v>-6.72</v>
       </c>
-      <c r="L39" s="488">
+      <c r="L39" s="485">
         <v>-10.65</v>
       </c>
-      <c r="M39" s="483">
+      <c r="M39" s="486">
         <v>-13.72</v>
       </c>
-      <c r="N39" s="490">
+      <c r="N39" s="487">
         <v>-12.84</v>
       </c>
-      <c r="O39" s="491">
+      <c r="O39" s="488">
         <v>-13.23</v>
       </c>
-      <c r="P39" s="484">
+      <c r="P39" s="490">
         <v>-12.03</v>
       </c>
-      <c r="Q39" s="489">
+      <c r="Q39" s="491">
         <v>-11.64</v>
       </c>
-      <c r="R39" s="485">
+      <c r="R39" s="492">
         <v>-12.98</v>
       </c>
-      <c r="S39" s="486">
+      <c r="S39" s="493">
         <v>-13.62</v>
       </c>
-      <c r="T39" s="492">
+      <c r="T39" s="494">
         <v>-14.79</v>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       <c r="C40" t="str">
         <v>300830</v>
       </c>
-      <c r="D40" s="496" t="str">
+      <c r="D40" s="505" t="str">
         <v>净卖: -2824.56万</v>
       </c>
       <c r="E40">
@@ -12397,40 +12397,40 @@
       <c r="H40">
         <v>3.71</v>
       </c>
-      <c r="I40" s="502">
+      <c r="I40" s="506">
         <v>15.71</v>
       </c>
-      <c r="J40" s="503">
+      <c r="J40" s="497">
         <v>10.42</v>
       </c>
-      <c r="K40" s="497">
+      <c r="K40" s="498">
         <v>3.42</v>
       </c>
-      <c r="L40" s="504">
+      <c r="L40" s="499">
         <v>5.52</v>
       </c>
-      <c r="M40" s="498">
+      <c r="M40" s="500">
         <v>2.18</v>
       </c>
-      <c r="N40" s="505">
+      <c r="N40" s="501">
         <v>10.96</v>
       </c>
-      <c r="O40" s="499">
+      <c r="O40" s="495">
         <v>10.03</v>
       </c>
-      <c r="P40" s="506">
+      <c r="P40" s="507">
         <v>10.11</v>
       </c>
-      <c r="Q40" s="500">
+      <c r="Q40" s="502">
         <v>10.42</v>
       </c>
-      <c r="R40" s="501">
+      <c r="R40" s="503">
         <v>5.37</v>
       </c>
-      <c r="S40" s="507">
+      <c r="S40" s="496">
         <v>0.39</v>
       </c>
-      <c r="T40" s="495">
+      <c r="T40" s="504">
         <v>-14.93</v>
       </c>
     </row>
@@ -12444,7 +12444,7 @@
       <c r="C41" t="str">
         <v>600135</v>
       </c>
-      <c r="D41" s="519" t="str">
+      <c r="D41" s="514" t="str">
         <v>净买: 5244.18万</v>
       </c>
       <c r="E41">
@@ -12459,40 +12459,40 @@
       <c r="H41">
         <v>3.48</v>
       </c>
-      <c r="I41" s="515">
+      <c r="I41" s="509">
         <v>6.35</v>
       </c>
-      <c r="J41" s="520">
+      <c r="J41" s="517">
         <v>5.77</v>
       </c>
-      <c r="K41" s="508">
+      <c r="K41" s="515">
         <v>7.88</v>
       </c>
-      <c r="L41" s="509">
+      <c r="L41" s="513">
         <v>2.21</v>
       </c>
-      <c r="M41" s="510">
+      <c r="M41" s="516">
         <v>0.38</v>
       </c>
-      <c r="N41" s="511">
+      <c r="N41" s="510">
         <v>1.44</v>
       </c>
-      <c r="O41" s="512">
+      <c r="O41" s="518">
         <v>1.54</v>
       </c>
-      <c r="P41" s="516">
+      <c r="P41" s="511">
         <v>-0.77</v>
       </c>
-      <c r="Q41" s="517">
+      <c r="Q41" s="519">
         <v>2.98</v>
       </c>
-      <c r="R41" s="513">
+      <c r="R41" s="520">
         <v>4.42</v>
       </c>
-      <c r="S41" s="514">
+      <c r="S41" s="508">
         <v>10.19</v>
       </c>
-      <c r="T41" s="518">
+      <c r="T41" s="512">
         <v>7.02</v>
       </c>
     </row>
@@ -12506,7 +12506,7 @@
       <c r="C42" t="str">
         <v>603629</v>
       </c>
-      <c r="D42" s="523" t="str">
+      <c r="D42" s="521" t="str">
         <v>净卖: -6126.05万</v>
       </c>
       <c r="E42">
@@ -12521,40 +12521,40 @@
       <c r="H42">
         <v>2.1</v>
       </c>
-      <c r="I42" s="524">
+      <c r="I42" s="531">
         <v>-11.86</v>
       </c>
-      <c r="J42" s="525">
+      <c r="J42" s="532">
         <v>-17.19</v>
       </c>
-      <c r="K42" s="526">
+      <c r="K42" s="533">
         <v>-18.01</v>
       </c>
       <c r="L42" s="527">
         <v>-9.81</v>
       </c>
-      <c r="M42" s="521">
+      <c r="M42" s="528">
         <v>-4.96</v>
       </c>
-      <c r="N42" s="528">
+      <c r="N42" s="529">
         <v>-7.22</v>
       </c>
-      <c r="O42" s="531">
+      <c r="O42" s="522">
         <v>-7.38</v>
       </c>
-      <c r="P42" s="529">
+      <c r="P42" s="523">
         <v>-7.57</v>
       </c>
-      <c r="Q42" s="532">
+      <c r="Q42" s="524">
         <v>-5.22</v>
       </c>
       <c r="R42" s="530">
         <v>-13.29</v>
       </c>
-      <c r="S42" s="533">
+      <c r="S42" s="525">
         <v>-14.5</v>
       </c>
-      <c r="T42" s="522">
+      <c r="T42" s="526">
         <v>51.71</v>
       </c>
     </row>
@@ -12568,7 +12568,7 @@
       <c r="C43" t="str">
         <v>002560</v>
       </c>
-      <c r="D43" s="538" t="str">
+      <c r="D43" s="546" t="str">
         <v>净买: 8507.98万</v>
       </c>
       <c r="E43">
@@ -12583,37 +12583,37 @@
       <c r="H43">
         <v>5.38</v>
       </c>
-      <c r="I43" s="543">
+      <c r="I43" s="540">
         <v>4.4</v>
       </c>
-      <c r="J43" s="544">
+      <c r="J43" s="542">
         <v>14.86</v>
       </c>
-      <c r="K43" s="537">
+      <c r="K43" s="543">
         <v>10.99</v>
       </c>
-      <c r="L43" s="546">
+      <c r="L43" s="534">
         <v>16.53</v>
       </c>
-      <c r="M43" s="534">
+      <c r="M43" s="535">
         <v>19.17</v>
       </c>
-      <c r="N43" s="539">
+      <c r="N43" s="544">
         <v>16.71</v>
       </c>
-      <c r="O43" s="540">
+      <c r="O43" s="536">
         <v>19.35</v>
       </c>
-      <c r="P43" s="535">
+      <c r="P43" s="537">
         <v>25.59</v>
       </c>
-      <c r="Q43" s="541">
+      <c r="Q43" s="538">
         <v>21.46</v>
       </c>
-      <c r="R43" s="542">
+      <c r="R43" s="541">
         <v>23.48</v>
       </c>
-      <c r="S43" s="536">
+      <c r="S43" s="539">
         <v>22.34</v>
       </c>
       <c r="T43" s="545">
@@ -12630,7 +12630,7 @@
       <c r="C44" t="str">
         <v>002560</v>
       </c>
-      <c r="D44" s="551" t="str">
+      <c r="D44" s="558" t="str">
         <v>净买: 3378.02万</v>
       </c>
       <c r="E44">
@@ -12645,38 +12645,38 @@
       <c r="H44">
         <v>5.51</v>
       </c>
-      <c r="I44" s="556">
+      <c r="I44" s="555">
         <v>-8.42</v>
       </c>
-      <c r="J44" s="552">
+      <c r="J44" s="556">
         <v>-3.85</v>
       </c>
-      <c r="K44" s="557">
+      <c r="K44" s="547">
         <v>-1.67</v>
       </c>
-      <c r="L44" s="558">
+      <c r="L44" s="548">
         <v>-3.7</v>
       </c>
       <c r="M44" s="549">
         <v>-1.52</v>
       </c>
-      <c r="N44" s="553">
+      <c r="N44" s="550">
         <v>3.63</v>
       </c>
-      <c r="O44" s="547">
+      <c r="O44" s="557">
         <v>0.22</v>
       </c>
-      <c r="P44" s="554">
+      <c r="P44" s="551">
         <v>1.89</v>
       </c>
-      <c r="Q44" s="548">
+      <c r="Q44" s="552">
         <v>0.94</v>
       </c>
-      <c r="R44" s="555">
+      <c r="R44" s="553">
         <v>0.73</v>
       </c>
       <c r="S44" t="str"/>
-      <c r="T44" s="550">
+      <c r="T44" s="554">
         <v>0.73</v>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       <c r="C45" t="str">
         <v>603629</v>
       </c>
-      <c r="D45" s="561" t="str">
+      <c r="D45" s="564" t="str">
         <v>净卖: -1.16亿</v>
       </c>
       <c r="E45">
@@ -12705,32 +12705,32 @@
       <c r="H45">
         <v>1.45</v>
       </c>
-      <c r="I45" s="564">
+      <c r="I45" s="566">
         <v>4.48</v>
       </c>
-      <c r="J45" s="562">
+      <c r="J45" s="565">
         <v>1.76</v>
       </c>
-      <c r="K45" s="565">
+      <c r="K45" s="560">
         <v>1.76</v>
       </c>
-      <c r="L45" s="559">
+      <c r="L45" s="567">
         <v>11.94</v>
       </c>
-      <c r="M45" s="560">
+      <c r="M45" s="561">
         <v>23.14</v>
       </c>
-      <c r="N45" s="566">
+      <c r="N45" s="563">
         <v>34.21</v>
       </c>
-      <c r="O45" s="567">
+      <c r="O45" s="559">
         <v>47.63</v>
       </c>
       <c r="P45" t="str"/>
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="563">
+      <c r="T45" s="562">
         <v>47.63</v>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       <c r="C46" t="str">
         <v>603629</v>
       </c>
-      <c r="D46" s="570" t="str">
+      <c r="D46" s="569" t="str">
         <v>净卖: -2.49亿</v>
       </c>
       <c r="E46">
@@ -12759,13 +12759,13 @@
       <c r="H46">
         <v>2</v>
       </c>
-      <c r="I46" s="571">
+      <c r="I46" s="570">
         <v>7.85</v>
       </c>
-      <c r="J46" s="572">
+      <c r="J46" s="571">
         <v>17.54</v>
       </c>
-      <c r="K46" s="568">
+      <c r="K46" s="572">
         <v>29.29</v>
       </c>
       <c r="L46" t="str"/>
@@ -12776,7 +12776,7 @@
       <c r="Q46" t="str"/>
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
-      <c r="T46" s="569">
+      <c r="T46" s="568">
         <v>29.29</v>
       </c>
     </row>
@@ -12959,40 +12959,40 @@
       <c r="F51" t="str"/>
       <c r="G51" t="str"/>
       <c r="H51" t="str"/>
-      <c r="I51" s="582">
+      <c r="I51" s="584">
         <v>68.75</v>
       </c>
-      <c r="J51" s="585">
+      <c r="J51" s="586">
         <v>68.89</v>
       </c>
-      <c r="K51" s="579">
+      <c r="K51" s="589">
         <v>66.67</v>
       </c>
-      <c r="L51" s="583">
+      <c r="L51" s="587">
         <v>59.09</v>
       </c>
-      <c r="M51" s="580">
+      <c r="M51" s="590">
         <v>56.82</v>
       </c>
-      <c r="N51" s="586">
+      <c r="N51" s="579">
         <v>59.09</v>
       </c>
-      <c r="O51" s="584">
+      <c r="O51" s="580">
         <v>61.36</v>
       </c>
-      <c r="P51" s="588">
+      <c r="P51" s="581">
         <v>60.47</v>
       </c>
-      <c r="Q51" s="581">
+      <c r="Q51" s="582">
         <v>60.47</v>
       </c>
-      <c r="R51" s="589">
+      <c r="R51" s="585">
         <v>62.79</v>
       </c>
-      <c r="S51" s="590">
+      <c r="S51" s="583">
         <v>61.9</v>
       </c>
-      <c r="T51" s="587">
+      <c r="T51" s="588">
         <v>60</v>
       </c>
     </row>
@@ -13007,40 +13007,40 @@
       <c r="F52" t="str"/>
       <c r="G52" t="str"/>
       <c r="H52" t="str"/>
-      <c r="I52" s="598">
+      <c r="I52" s="591">
         <v>5.22</v>
       </c>
-      <c r="J52" s="601">
+      <c r="J52" s="592">
         <v>5.43</v>
       </c>
-      <c r="K52" s="594">
+      <c r="K52" s="596">
         <v>5.9</v>
       </c>
-      <c r="L52" s="595">
+      <c r="L52" s="593">
         <v>4.64</v>
       </c>
-      <c r="M52" s="602">
+      <c r="M52" s="597">
         <v>3.87</v>
       </c>
-      <c r="N52" s="591">
+      <c r="N52" s="598">
         <v>4.83</v>
       </c>
-      <c r="O52" s="592">
+      <c r="O52" s="601">
         <v>5.37</v>
       </c>
-      <c r="P52" s="596">
+      <c r="P52" s="599">
         <v>5.02</v>
       </c>
-      <c r="Q52" s="599">
+      <c r="Q52" s="602">
         <v>5.43</v>
       </c>
-      <c r="R52" s="593">
+      <c r="R52" s="594">
         <v>6.06</v>
       </c>
-      <c r="S52" s="597">
+      <c r="S52" s="600">
         <v>7.45</v>
       </c>
-      <c r="T52" s="600">
+      <c r="T52" s="595">
         <v>12.28</v>
       </c>
     </row>
